--- a/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>VIPS</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14243300</v>
+        <v>15689200</v>
       </c>
       <c r="E8" s="3">
-        <v>16163600</v>
+        <v>14340300</v>
       </c>
       <c r="F8" s="3">
-        <v>14064600</v>
+        <v>16273600</v>
       </c>
       <c r="G8" s="3">
-        <v>12840700</v>
+        <v>14160400</v>
       </c>
       <c r="H8" s="3">
-        <v>11671100</v>
+        <v>12928100</v>
       </c>
       <c r="I8" s="3">
-        <v>10067700</v>
+        <v>11750500</v>
       </c>
       <c r="J8" s="3">
+        <v>10136300</v>
+      </c>
+      <c r="K8" s="3">
         <v>7814100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5596300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3621100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1585200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>99300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>11258500</v>
+        <v>12113500</v>
       </c>
       <c r="E9" s="3">
-        <v>12973000</v>
+        <v>11335200</v>
       </c>
       <c r="F9" s="3">
-        <v>11125500</v>
+        <v>13061400</v>
       </c>
       <c r="G9" s="3">
-        <v>9985100</v>
+        <v>11201300</v>
       </c>
       <c r="H9" s="3">
-        <v>9314200</v>
+        <v>10053100</v>
       </c>
       <c r="I9" s="3">
-        <v>7817900</v>
+        <v>9377600</v>
       </c>
       <c r="J9" s="3">
+        <v>7871100</v>
+      </c>
+      <c r="K9" s="3">
         <v>5936700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4218700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2720700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1204200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>77100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26700</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2984700</v>
+        <v>3575700</v>
       </c>
       <c r="E10" s="3">
-        <v>3190600</v>
+        <v>3005100</v>
       </c>
       <c r="F10" s="3">
-        <v>2939100</v>
+        <v>3212300</v>
       </c>
       <c r="G10" s="3">
-        <v>2855500</v>
+        <v>2959100</v>
       </c>
       <c r="H10" s="3">
-        <v>2356900</v>
+        <v>2875000</v>
       </c>
       <c r="I10" s="3">
-        <v>2249900</v>
+        <v>2372900</v>
       </c>
       <c r="J10" s="3">
+        <v>2265200</v>
+      </c>
+      <c r="K10" s="3">
         <v>1877400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1377600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>900400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>381000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>22200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6300</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -896,15 +909,18 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3">
         <v>1900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>700</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,51 +960,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>46000</v>
+        <v>2700</v>
       </c>
       <c r="E14" s="3">
-        <v>57300</v>
+        <v>46300</v>
       </c>
       <c r="F14" s="3">
+        <v>57700</v>
+      </c>
+      <c r="G14" s="3">
         <v>6000</v>
       </c>
-      <c r="G14" s="3">
-        <v>56000</v>
-      </c>
       <c r="H14" s="3">
+        <v>56400</v>
+      </c>
+      <c r="I14" s="3">
         <v>2800</v>
       </c>
-      <c r="I14" s="3">
-        <v>18400</v>
-      </c>
       <c r="J14" s="3">
+        <v>18500</v>
+      </c>
+      <c r="K14" s="3">
         <v>15800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1001,36 +1023,39 @@
       <c r="F15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G15" s="3">
-        <v>114700</v>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H15" s="3">
-        <v>106400</v>
+        <v>115400</v>
       </c>
       <c r="I15" s="3">
-        <v>99500</v>
+        <v>107100</v>
       </c>
       <c r="J15" s="3">
+        <v>100200</v>
+      </c>
+      <c r="K15" s="3">
         <v>84400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>40600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>17200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13400500</v>
+        <v>14426200</v>
       </c>
       <c r="E17" s="3">
-        <v>15450100</v>
+        <v>13491700</v>
       </c>
       <c r="F17" s="3">
-        <v>13261400</v>
+        <v>15555200</v>
       </c>
       <c r="G17" s="3">
-        <v>12199200</v>
+        <v>13351700</v>
       </c>
       <c r="H17" s="3">
-        <v>11339500</v>
+        <v>12282200</v>
       </c>
       <c r="I17" s="3">
-        <v>9714600</v>
+        <v>11416700</v>
       </c>
       <c r="J17" s="3">
+        <v>9780700</v>
+      </c>
+      <c r="K17" s="3">
         <v>7456100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5322000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3491600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1534900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>101400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>48700</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>842800</v>
+        <v>1263000</v>
       </c>
       <c r="E18" s="3">
-        <v>713500</v>
+        <v>848500</v>
       </c>
       <c r="F18" s="3">
-        <v>803200</v>
+        <v>718400</v>
       </c>
       <c r="G18" s="3">
-        <v>641500</v>
+        <v>808700</v>
       </c>
       <c r="H18" s="3">
-        <v>331500</v>
+        <v>645900</v>
       </c>
       <c r="I18" s="3">
-        <v>353100</v>
+        <v>333800</v>
       </c>
       <c r="J18" s="3">
+        <v>355500</v>
+      </c>
+      <c r="K18" s="3">
         <v>358100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>274300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>129600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>50300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15600</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>275900</v>
+        <v>128600</v>
       </c>
       <c r="E20" s="3">
-        <v>99400</v>
+        <v>277800</v>
       </c>
       <c r="F20" s="3">
-        <v>175300</v>
+        <v>100100</v>
       </c>
       <c r="G20" s="3">
-        <v>52900</v>
+        <v>176500</v>
       </c>
       <c r="H20" s="3">
-        <v>69800</v>
+        <v>53200</v>
       </c>
       <c r="I20" s="3">
-        <v>9100</v>
+        <v>70300</v>
       </c>
       <c r="J20" s="3">
+        <v>9200</v>
+      </c>
+      <c r="K20" s="3">
         <v>21800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>23000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>48200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>15900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>1313700</v>
+      <c r="D21" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E21" s="3">
-        <v>986800</v>
+        <v>1323000</v>
       </c>
       <c r="F21" s="3">
-        <v>1135800</v>
+        <v>993800</v>
       </c>
       <c r="G21" s="3">
-        <v>825500</v>
+        <v>1143700</v>
       </c>
       <c r="H21" s="3">
-        <v>524200</v>
+        <v>831400</v>
       </c>
       <c r="I21" s="3">
-        <v>516400</v>
+        <v>527900</v>
       </c>
       <c r="J21" s="3">
+        <v>520200</v>
+      </c>
+      <c r="K21" s="3">
         <v>519600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>378000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>234200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>67600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-15300</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="E22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F22" s="3">
         <v>2000</v>
       </c>
-      <c r="F22" s="3">
-        <v>9300</v>
-      </c>
       <c r="G22" s="3">
+        <v>9400</v>
+      </c>
+      <c r="H22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>22200</v>
+      </c>
+      <c r="J22" s="3">
+        <v>11500</v>
+      </c>
+      <c r="K22" s="3">
+        <v>11800</v>
+      </c>
+      <c r="L22" s="3">
         <v>11900</v>
       </c>
-      <c r="H22" s="3">
-        <v>22100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>11400</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="M22" s="3">
         <v>11800</v>
       </c>
-      <c r="K22" s="3">
-        <v>11900</v>
-      </c>
-      <c r="L22" s="3">
-        <v>11800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1115300</v>
+        <v>1388400</v>
       </c>
       <c r="E23" s="3">
-        <v>811000</v>
+        <v>1122900</v>
       </c>
       <c r="F23" s="3">
-        <v>969200</v>
+        <v>816500</v>
       </c>
       <c r="G23" s="3">
-        <v>682500</v>
+        <v>975800</v>
       </c>
       <c r="H23" s="3">
-        <v>379300</v>
+        <v>687100</v>
       </c>
       <c r="I23" s="3">
-        <v>350800</v>
+        <v>381900</v>
       </c>
       <c r="J23" s="3">
+        <v>353200</v>
+      </c>
+      <c r="K23" s="3">
         <v>368100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>285400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>166000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>66200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15600</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>242900</v>
+        <v>259400</v>
       </c>
       <c r="E24" s="3">
-        <v>168800</v>
+        <v>244500</v>
       </c>
       <c r="F24" s="3">
-        <v>156000</v>
+        <v>170000</v>
       </c>
       <c r="G24" s="3">
-        <v>135800</v>
+        <v>157100</v>
       </c>
       <c r="H24" s="3">
-        <v>78200</v>
+        <v>136700</v>
       </c>
       <c r="I24" s="3">
-        <v>86500</v>
+        <v>78800</v>
       </c>
       <c r="J24" s="3">
+        <v>87000</v>
+      </c>
+      <c r="K24" s="3">
         <v>83100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>63700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>38400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>17300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>872400</v>
+        <v>1129000</v>
       </c>
       <c r="E26" s="3">
-        <v>642200</v>
+        <v>878400</v>
       </c>
       <c r="F26" s="3">
-        <v>813200</v>
+        <v>646500</v>
       </c>
       <c r="G26" s="3">
-        <v>546700</v>
+        <v>818700</v>
       </c>
       <c r="H26" s="3">
-        <v>301100</v>
+        <v>550400</v>
       </c>
       <c r="I26" s="3">
-        <v>264400</v>
+        <v>303100</v>
       </c>
       <c r="J26" s="3">
+        <v>266200</v>
+      </c>
+      <c r="K26" s="3">
         <v>285000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>221700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>127600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>48900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15600</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>869700</v>
+        <v>1128400</v>
       </c>
       <c r="E27" s="3">
-        <v>646400</v>
+        <v>875700</v>
       </c>
       <c r="F27" s="3">
-        <v>815600</v>
+        <v>650800</v>
       </c>
       <c r="G27" s="3">
-        <v>554600</v>
+        <v>821200</v>
       </c>
       <c r="H27" s="3">
-        <v>293900</v>
+        <v>558400</v>
       </c>
       <c r="I27" s="3">
-        <v>269200</v>
+        <v>295900</v>
       </c>
       <c r="J27" s="3">
+        <v>271000</v>
+      </c>
+      <c r="K27" s="3">
         <v>281200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>221300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>131700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>48900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-22800</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-275900</v>
+        <v>-128600</v>
       </c>
       <c r="E32" s="3">
-        <v>-99400</v>
+        <v>-277800</v>
       </c>
       <c r="F32" s="3">
-        <v>-175300</v>
+        <v>-100100</v>
       </c>
       <c r="G32" s="3">
-        <v>-52900</v>
+        <v>-176500</v>
       </c>
       <c r="H32" s="3">
-        <v>-69800</v>
+        <v>-53200</v>
       </c>
       <c r="I32" s="3">
-        <v>-9100</v>
+        <v>-70300</v>
       </c>
       <c r="J32" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-21800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-23000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-48200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-15900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>869700</v>
+        <v>1128400</v>
       </c>
       <c r="E33" s="3">
-        <v>646400</v>
+        <v>875700</v>
       </c>
       <c r="F33" s="3">
-        <v>815600</v>
+        <v>650800</v>
       </c>
       <c r="G33" s="3">
-        <v>554600</v>
+        <v>821200</v>
       </c>
       <c r="H33" s="3">
-        <v>293900</v>
+        <v>558400</v>
       </c>
       <c r="I33" s="3">
-        <v>269200</v>
+        <v>295900</v>
       </c>
       <c r="J33" s="3">
+        <v>271000</v>
+      </c>
+      <c r="K33" s="3">
         <v>281200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>221300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>131700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>48900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-22800</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>869700</v>
+        <v>1128400</v>
       </c>
       <c r="E35" s="3">
-        <v>646400</v>
+        <v>875700</v>
       </c>
       <c r="F35" s="3">
-        <v>815600</v>
+        <v>650800</v>
       </c>
       <c r="G35" s="3">
-        <v>554600</v>
+        <v>821200</v>
       </c>
       <c r="H35" s="3">
-        <v>293900</v>
+        <v>558400</v>
       </c>
       <c r="I35" s="3">
-        <v>269200</v>
+        <v>295900</v>
       </c>
       <c r="J35" s="3">
+        <v>271000</v>
+      </c>
+      <c r="K35" s="3">
         <v>281200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>221300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>131700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>48900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-22800</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,292 +1986,311 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3029300</v>
+        <v>3533200</v>
       </c>
       <c r="E41" s="3">
-        <v>2250300</v>
+        <v>3049900</v>
       </c>
       <c r="F41" s="3">
-        <v>1656300</v>
+        <v>2265700</v>
       </c>
       <c r="G41" s="3">
-        <v>907700</v>
+        <v>1667600</v>
       </c>
       <c r="H41" s="3">
-        <v>1317400</v>
+        <v>913900</v>
       </c>
       <c r="I41" s="3">
-        <v>1377200</v>
+        <v>1326300</v>
       </c>
       <c r="J41" s="3">
+        <v>1386600</v>
+      </c>
+      <c r="K41" s="3">
         <v>567500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>462800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>750000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>50900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6500</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>220400</v>
+        <v>275700</v>
       </c>
       <c r="E42" s="3">
-        <v>743100</v>
+        <v>221900</v>
       </c>
       <c r="F42" s="3">
-        <v>1011900</v>
+        <v>748200</v>
       </c>
       <c r="G42" s="3">
-        <v>421500</v>
+        <v>1018800</v>
       </c>
       <c r="H42" s="3">
-        <v>320500</v>
+        <v>424400</v>
       </c>
       <c r="I42" s="3">
-        <v>34000</v>
+        <v>322700</v>
       </c>
       <c r="J42" s="3">
+        <v>34200</v>
+      </c>
+      <c r="K42" s="3">
         <v>92800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>251600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>590000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>58700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>12400</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>485900</v>
+        <v>505400</v>
       </c>
       <c r="E43" s="3">
-        <v>472800</v>
+        <v>489200</v>
       </c>
       <c r="F43" s="3">
-        <v>411700</v>
+        <v>476000</v>
       </c>
       <c r="G43" s="3">
-        <v>628000</v>
+        <v>414500</v>
       </c>
       <c r="H43" s="3">
-        <v>1325300</v>
+        <v>632200</v>
       </c>
       <c r="I43" s="3">
-        <v>1172000</v>
+        <v>1334300</v>
       </c>
       <c r="J43" s="3">
+        <v>1180000</v>
+      </c>
+      <c r="K43" s="3">
         <v>627400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>306300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>155700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>761600</v>
+        <v>784700</v>
       </c>
       <c r="E44" s="3">
-        <v>947900</v>
+        <v>766800</v>
       </c>
       <c r="F44" s="3">
-        <v>1055300</v>
+        <v>954400</v>
       </c>
       <c r="G44" s="3">
-        <v>1064400</v>
+        <v>1062500</v>
       </c>
       <c r="H44" s="3">
-        <v>741200</v>
+        <v>1071600</v>
       </c>
       <c r="I44" s="3">
-        <v>961100</v>
+        <v>746300</v>
       </c>
       <c r="J44" s="3">
+        <v>967600</v>
+      </c>
+      <c r="K44" s="3">
         <v>683300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>635700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>561800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>41100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>20700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10100</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>160800</v>
+        <v>122700</v>
       </c>
       <c r="E45" s="3">
-        <v>120700</v>
+        <v>161900</v>
       </c>
       <c r="F45" s="3">
-        <v>169100</v>
+        <v>121500</v>
       </c>
       <c r="G45" s="3">
-        <v>158200</v>
+        <v>170300</v>
       </c>
       <c r="H45" s="3">
-        <v>68800</v>
+        <v>159200</v>
       </c>
       <c r="I45" s="3">
-        <v>34300</v>
+        <v>69200</v>
       </c>
       <c r="J45" s="3">
+        <v>34500</v>
+      </c>
+      <c r="K45" s="3">
         <v>42400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>52700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4400</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4658100</v>
+        <v>5221700</v>
       </c>
       <c r="E46" s="3">
-        <v>4534800</v>
+        <v>4689800</v>
       </c>
       <c r="F46" s="3">
-        <v>4304400</v>
+        <v>4565700</v>
       </c>
       <c r="G46" s="3">
-        <v>3179700</v>
+        <v>4333700</v>
       </c>
       <c r="H46" s="3">
-        <v>3773100</v>
+        <v>3201400</v>
       </c>
       <c r="I46" s="3">
-        <v>3578500</v>
+        <v>3798800</v>
       </c>
       <c r="J46" s="3">
+        <v>3602900</v>
+      </c>
+      <c r="K46" s="3">
         <v>2013300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1691700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2069800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>157700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>54800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>23000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>666000</v>
+        <v>705100</v>
       </c>
       <c r="E47" s="3">
-        <v>684800</v>
+        <v>670500</v>
       </c>
       <c r="F47" s="3">
-        <v>664300</v>
+        <v>689500</v>
       </c>
       <c r="G47" s="3">
-        <v>720500</v>
+        <v>668800</v>
       </c>
       <c r="H47" s="3">
-        <v>295200</v>
+        <v>725400</v>
       </c>
       <c r="I47" s="3">
-        <v>82900</v>
+        <v>297200</v>
       </c>
       <c r="J47" s="3">
+        <v>83400</v>
+      </c>
+      <c r="K47" s="3">
         <v>138700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>140900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>61100</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
@@ -2194,93 +2298,102 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2363600</v>
+        <v>2424000</v>
       </c>
       <c r="E48" s="3">
-        <v>2143700</v>
+        <v>2379700</v>
       </c>
       <c r="F48" s="3">
-        <v>2094000</v>
+        <v>2158300</v>
       </c>
       <c r="G48" s="3">
-        <v>1791200</v>
+        <v>2108300</v>
       </c>
       <c r="H48" s="3">
-        <v>1178000</v>
+        <v>1803400</v>
       </c>
       <c r="I48" s="3">
-        <v>919700</v>
+        <v>1186000</v>
       </c>
       <c r="J48" s="3">
+        <v>926000</v>
+      </c>
+      <c r="K48" s="3">
         <v>616900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>410600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>598500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1300</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>151300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>151800</v>
+      </c>
+      <c r="F49" s="3">
+        <v>126500</v>
+      </c>
+      <c r="G49" s="3">
+        <v>128800</v>
+      </c>
+      <c r="H49" s="3">
+        <v>79800</v>
+      </c>
+      <c r="I49" s="3">
+        <v>100100</v>
+      </c>
+      <c r="J49" s="3">
+        <v>106800</v>
+      </c>
+      <c r="K49" s="3">
         <v>150800</v>
       </c>
-      <c r="E49" s="3">
-        <v>125700</v>
-      </c>
-      <c r="F49" s="3">
-        <v>128000</v>
-      </c>
-      <c r="G49" s="3">
-        <v>79300</v>
-      </c>
-      <c r="H49" s="3">
-        <v>99400</v>
-      </c>
-      <c r="I49" s="3">
-        <v>106100</v>
-      </c>
-      <c r="J49" s="3">
-        <v>150800</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>118800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>172100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>800</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1202500</v>
+        <v>1552300</v>
       </c>
       <c r="E52" s="3">
-        <v>1111600</v>
+        <v>1210700</v>
       </c>
       <c r="F52" s="3">
-        <v>947900</v>
+        <v>1119200</v>
       </c>
       <c r="G52" s="3">
-        <v>937600</v>
+        <v>954400</v>
       </c>
       <c r="H52" s="3">
-        <v>669300</v>
+        <v>944000</v>
       </c>
       <c r="I52" s="3">
-        <v>557500</v>
+        <v>673900</v>
       </c>
       <c r="J52" s="3">
+        <v>561300</v>
+      </c>
+      <c r="K52" s="3">
         <v>545400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>427000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>64500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>600</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9040900</v>
+        <v>10054300</v>
       </c>
       <c r="E54" s="3">
-        <v>8600700</v>
+        <v>9102400</v>
       </c>
       <c r="F54" s="3">
-        <v>8138500</v>
+        <v>8659200</v>
       </c>
       <c r="G54" s="3">
-        <v>6708300</v>
+        <v>8194000</v>
       </c>
       <c r="H54" s="3">
-        <v>6015100</v>
+        <v>6754000</v>
       </c>
       <c r="I54" s="3">
-        <v>5244700</v>
+        <v>6056100</v>
       </c>
       <c r="J54" s="3">
+        <v>5280400</v>
+      </c>
+      <c r="K54" s="3">
         <v>3465000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2788900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2653900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>163100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>57200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>24400</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,176 +2654,189 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2073700</v>
+        <v>2399400</v>
       </c>
       <c r="E57" s="3">
-        <v>1815100</v>
+        <v>2087800</v>
       </c>
       <c r="F57" s="3">
-        <v>2097600</v>
+        <v>1827400</v>
       </c>
       <c r="G57" s="3">
-        <v>1904400</v>
+        <v>2111900</v>
       </c>
       <c r="H57" s="3">
-        <v>1605900</v>
+        <v>1917400</v>
       </c>
       <c r="I57" s="3">
-        <v>1580300</v>
+        <v>1616800</v>
       </c>
       <c r="J57" s="3">
+        <v>1591100</v>
+      </c>
+      <c r="K57" s="3">
         <v>1150700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>925000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>958300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>72500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12800</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>371100</v>
+        <v>198200</v>
       </c>
       <c r="E58" s="3">
-        <v>272700</v>
+        <v>373600</v>
       </c>
       <c r="F58" s="3">
-        <v>144100</v>
+        <v>274600</v>
       </c>
       <c r="G58" s="3">
-        <v>151000</v>
+        <v>145100</v>
       </c>
       <c r="H58" s="3">
-        <v>916800</v>
+        <v>152000</v>
       </c>
       <c r="I58" s="3">
-        <v>230200</v>
+        <v>923000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>231800</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>13200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="s">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>1800</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1494100</v>
+        <v>1659800</v>
       </c>
       <c r="E59" s="3">
-        <v>1470700</v>
+        <v>1504300</v>
       </c>
       <c r="F59" s="3">
-        <v>1426900</v>
+        <v>1480700</v>
       </c>
       <c r="G59" s="3">
-        <v>1248200</v>
+        <v>1436700</v>
       </c>
       <c r="H59" s="3">
-        <v>1060000</v>
+        <v>1256700</v>
       </c>
       <c r="I59" s="3">
-        <v>848500</v>
+        <v>1067200</v>
       </c>
       <c r="J59" s="3">
+        <v>854300</v>
+      </c>
+      <c r="K59" s="3">
         <v>863000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>755300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>998000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>53500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7400</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3938900</v>
+        <v>4257400</v>
       </c>
       <c r="E60" s="3">
-        <v>3558500</v>
+        <v>3965700</v>
       </c>
       <c r="F60" s="3">
-        <v>3668600</v>
+        <v>3582700</v>
       </c>
       <c r="G60" s="3">
-        <v>3303700</v>
+        <v>3693600</v>
       </c>
       <c r="H60" s="3">
-        <v>3582600</v>
+        <v>3326100</v>
       </c>
       <c r="I60" s="3">
-        <v>2659100</v>
+        <v>3607000</v>
       </c>
       <c r="J60" s="3">
+        <v>2677200</v>
+      </c>
+      <c r="K60" s="3">
         <v>2013700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1693500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1589900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>126100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>45400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21700</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2708,67 +2850,70 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>8900</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="I61" s="3">
-        <v>565400</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>569300</v>
+      </c>
+      <c r="K61" s="3">
         <v>605000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>564900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>603500</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>397200</v>
+        <v>436300</v>
       </c>
       <c r="E62" s="3">
-        <v>371200</v>
+        <v>399900</v>
       </c>
       <c r="F62" s="3">
-        <v>412300</v>
+        <v>373700</v>
       </c>
       <c r="G62" s="3">
-        <v>323500</v>
+        <v>415100</v>
       </c>
       <c r="H62" s="3">
-        <v>56000</v>
+        <v>325700</v>
       </c>
       <c r="I62" s="3">
-        <v>52400</v>
+        <v>56400</v>
       </c>
       <c r="J62" s="3">
+        <v>52800</v>
+      </c>
+      <c r="K62" s="3">
         <v>48000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>27600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>38000</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>8</v>
@@ -2776,9 +2921,12 @@
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4518500</v>
+        <v>4915900</v>
       </c>
       <c r="E66" s="3">
-        <v>4094700</v>
+        <v>4549200</v>
       </c>
       <c r="F66" s="3">
-        <v>4203600</v>
+        <v>4122600</v>
       </c>
       <c r="G66" s="3">
-        <v>3694400</v>
+        <v>4232200</v>
       </c>
       <c r="H66" s="3">
-        <v>3631600</v>
+        <v>3719600</v>
       </c>
       <c r="I66" s="3">
-        <v>3270900</v>
+        <v>3656300</v>
       </c>
       <c r="J66" s="3">
+        <v>3293100</v>
+      </c>
+      <c r="K66" s="3">
         <v>2673500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2296300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2254000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>126100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21700</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3086,11 +3253,14 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>8900</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3965700</v>
+        <v>5121100</v>
       </c>
       <c r="E72" s="3">
-        <v>3096000</v>
+        <v>3992700</v>
       </c>
       <c r="F72" s="3">
-        <v>2449600</v>
+        <v>3117000</v>
       </c>
       <c r="G72" s="3">
-        <v>1646500</v>
+        <v>2466300</v>
       </c>
       <c r="H72" s="3">
-        <v>1091900</v>
+        <v>1657700</v>
       </c>
       <c r="I72" s="3">
-        <v>773600</v>
+        <v>1099300</v>
       </c>
       <c r="J72" s="3">
+        <v>778900</v>
+      </c>
+      <c r="K72" s="3">
         <v>504400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>225000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-18800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-25300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-24200</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4522400</v>
+        <v>5138400</v>
       </c>
       <c r="E76" s="3">
-        <v>4506000</v>
+        <v>4553200</v>
       </c>
       <c r="F76" s="3">
-        <v>3935000</v>
+        <v>4536600</v>
       </c>
       <c r="G76" s="3">
-        <v>3013900</v>
+        <v>3961800</v>
       </c>
       <c r="H76" s="3">
-        <v>2383500</v>
+        <v>3034400</v>
       </c>
       <c r="I76" s="3">
-        <v>1973800</v>
+        <v>2399700</v>
       </c>
       <c r="J76" s="3">
+        <v>1987200</v>
+      </c>
+      <c r="K76" s="3">
         <v>791500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>492700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>399900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-6200</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>869700</v>
+        <v>1128400</v>
       </c>
       <c r="E81" s="3">
-        <v>646400</v>
+        <v>875700</v>
       </c>
       <c r="F81" s="3">
-        <v>815600</v>
+        <v>650800</v>
       </c>
       <c r="G81" s="3">
-        <v>554600</v>
+        <v>821200</v>
       </c>
       <c r="H81" s="3">
-        <v>293900</v>
+        <v>558400</v>
       </c>
       <c r="I81" s="3">
-        <v>269200</v>
+        <v>295900</v>
       </c>
       <c r="J81" s="3">
+        <v>271000</v>
+      </c>
+      <c r="K81" s="3">
         <v>281200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>221300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>131700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>48900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-22800</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>195200</v>
+      <c r="D83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E83" s="3">
-        <v>173900</v>
+        <v>196500</v>
       </c>
       <c r="F83" s="3">
-        <v>157300</v>
+        <v>175100</v>
       </c>
       <c r="G83" s="3">
-        <v>131200</v>
+        <v>158400</v>
       </c>
       <c r="H83" s="3">
-        <v>122900</v>
+        <v>132100</v>
       </c>
       <c r="I83" s="3">
-        <v>154300</v>
+        <v>123700</v>
       </c>
       <c r="J83" s="3">
+        <v>155300</v>
+      </c>
+      <c r="K83" s="3">
         <v>139800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>81300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>56500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1452600</v>
+        <v>2003900</v>
       </c>
       <c r="E89" s="3">
-        <v>931300</v>
+        <v>1462400</v>
       </c>
       <c r="F89" s="3">
-        <v>1632200</v>
+        <v>937600</v>
       </c>
       <c r="G89" s="3">
-        <v>1697000</v>
+        <v>1643300</v>
       </c>
       <c r="H89" s="3">
-        <v>793400</v>
+        <v>1708600</v>
       </c>
       <c r="I89" s="3">
-        <v>135500</v>
+        <v>798800</v>
       </c>
       <c r="J89" s="3">
+        <v>136400</v>
+      </c>
+      <c r="K89" s="3">
         <v>391000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>266600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>510800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>66500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>16000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>200</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-428400</v>
+        <v>-727200</v>
       </c>
       <c r="E91" s="3">
-        <v>-494100</v>
+        <v>-431300</v>
       </c>
       <c r="F91" s="3">
-        <v>-313700</v>
+        <v>-497500</v>
       </c>
       <c r="G91" s="3">
-        <v>-590700</v>
+        <v>-315800</v>
       </c>
       <c r="H91" s="3">
-        <v>-496300</v>
+        <v>-594700</v>
       </c>
       <c r="I91" s="3">
-        <v>-341700</v>
+        <v>-499600</v>
       </c>
       <c r="J91" s="3">
+        <v>-344000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-321700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-266200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1400</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>144900</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E94" s="3">
-        <v>-321200</v>
+        <v>145900</v>
       </c>
       <c r="F94" s="3">
-        <v>-924500</v>
+        <v>-323400</v>
       </c>
       <c r="G94" s="3">
-        <v>-1137900</v>
+        <v>-930700</v>
       </c>
       <c r="H94" s="3">
-        <v>-924300</v>
+        <v>-1145600</v>
       </c>
       <c r="I94" s="3">
-        <v>-280700</v>
+        <v>-930600</v>
       </c>
       <c r="J94" s="3">
+        <v>-282600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-230500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-408900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-665900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-48800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3500</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,8 +4220,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4029,9 +4262,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-769600</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E100" s="3">
-        <v>-8100</v>
+        <v>-774800</v>
       </c>
       <c r="F100" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="G100" s="3">
         <v>-2900</v>
       </c>
-      <c r="G100" s="3">
-        <v>-863900</v>
-      </c>
       <c r="H100" s="3">
-        <v>81000</v>
+        <v>-869800</v>
       </c>
       <c r="I100" s="3">
-        <v>990000</v>
+        <v>81600</v>
       </c>
       <c r="J100" s="3">
+        <v>996700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-54300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-75000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>603100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>14100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>9700</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>-8700</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E101" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1700</v>
       </c>
-      <c r="G101" s="3">
-        <v>-15500</v>
-      </c>
       <c r="H101" s="3">
-        <v>24500</v>
+        <v>-15600</v>
       </c>
       <c r="I101" s="3">
+        <v>24700</v>
+      </c>
+      <c r="J101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>13200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-15200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>819100</v>
+      <c r="D102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E102" s="3">
-        <v>602000</v>
+        <v>824700</v>
       </c>
       <c r="F102" s="3">
-        <v>703100</v>
+        <v>606100</v>
       </c>
       <c r="G102" s="3">
-        <v>-320200</v>
+        <v>707900</v>
       </c>
       <c r="H102" s="3">
-        <v>-25300</v>
+        <v>-322400</v>
       </c>
       <c r="I102" s="3">
-        <v>844000</v>
+        <v>-25500</v>
       </c>
       <c r="J102" s="3">
+        <v>849700</v>
+      </c>
+      <c r="K102" s="3">
         <v>108400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-204100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>432800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>32000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>11400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6400</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>VIPS</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>15689200</v>
+        <v>15592200</v>
       </c>
       <c r="E8" s="3">
-        <v>14340300</v>
+        <v>14251500</v>
       </c>
       <c r="F8" s="3">
-        <v>16273600</v>
+        <v>16173000</v>
       </c>
       <c r="G8" s="3">
-        <v>14160400</v>
+        <v>14072800</v>
       </c>
       <c r="H8" s="3">
-        <v>12928100</v>
+        <v>12848100</v>
       </c>
       <c r="I8" s="3">
-        <v>11750500</v>
+        <v>11677800</v>
       </c>
       <c r="J8" s="3">
-        <v>10136300</v>
+        <v>10073600</v>
       </c>
       <c r="K8" s="3">
         <v>7814100</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>12113500</v>
+        <v>12038600</v>
       </c>
       <c r="E9" s="3">
-        <v>11335200</v>
+        <v>11265100</v>
       </c>
       <c r="F9" s="3">
-        <v>13061400</v>
+        <v>12980600</v>
       </c>
       <c r="G9" s="3">
-        <v>11201300</v>
+        <v>11132000</v>
       </c>
       <c r="H9" s="3">
-        <v>10053100</v>
+        <v>9990900</v>
       </c>
       <c r="I9" s="3">
-        <v>9377600</v>
+        <v>9319600</v>
       </c>
       <c r="J9" s="3">
-        <v>7871100</v>
+        <v>7822400</v>
       </c>
       <c r="K9" s="3">
         <v>5936700</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3575700</v>
+        <v>3553600</v>
       </c>
       <c r="E10" s="3">
-        <v>3005100</v>
+        <v>2986500</v>
       </c>
       <c r="F10" s="3">
-        <v>3212300</v>
+        <v>3192400</v>
       </c>
       <c r="G10" s="3">
-        <v>2959100</v>
+        <v>2940800</v>
       </c>
       <c r="H10" s="3">
-        <v>2875000</v>
+        <v>2857200</v>
       </c>
       <c r="I10" s="3">
-        <v>2372900</v>
+        <v>2358200</v>
       </c>
       <c r="J10" s="3">
-        <v>2265200</v>
+        <v>2251200</v>
       </c>
       <c r="K10" s="3">
         <v>1877400</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2700</v>
+        <v>24200</v>
       </c>
       <c r="E14" s="3">
-        <v>46300</v>
+        <v>46000</v>
       </c>
       <c r="F14" s="3">
-        <v>57700</v>
+        <v>57300</v>
       </c>
       <c r="G14" s="3">
         <v>6000</v>
       </c>
       <c r="H14" s="3">
-        <v>56400</v>
+        <v>56100</v>
       </c>
       <c r="I14" s="3">
         <v>2800</v>
       </c>
       <c r="J14" s="3">
-        <v>18500</v>
+        <v>18400</v>
       </c>
       <c r="K14" s="3">
         <v>15800</v>
@@ -1027,13 +1027,13 @@
         <v>8</v>
       </c>
       <c r="H15" s="3">
-        <v>115400</v>
+        <v>114700</v>
       </c>
       <c r="I15" s="3">
-        <v>107100</v>
+        <v>106400</v>
       </c>
       <c r="J15" s="3">
-        <v>100200</v>
+        <v>99600</v>
       </c>
       <c r="K15" s="3">
         <v>84400</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14426200</v>
+        <v>14337000</v>
       </c>
       <c r="E17" s="3">
-        <v>13491700</v>
+        <v>13408300</v>
       </c>
       <c r="F17" s="3">
-        <v>15555200</v>
+        <v>15459000</v>
       </c>
       <c r="G17" s="3">
-        <v>13351700</v>
+        <v>13269100</v>
       </c>
       <c r="H17" s="3">
-        <v>12282200</v>
+        <v>12206200</v>
       </c>
       <c r="I17" s="3">
-        <v>11416700</v>
+        <v>11346100</v>
       </c>
       <c r="J17" s="3">
-        <v>9780700</v>
+        <v>9720200</v>
       </c>
       <c r="K17" s="3">
         <v>7456100</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1263000</v>
+        <v>1255200</v>
       </c>
       <c r="E18" s="3">
-        <v>848500</v>
+        <v>843300</v>
       </c>
       <c r="F18" s="3">
-        <v>718400</v>
+        <v>714000</v>
       </c>
       <c r="G18" s="3">
-        <v>808700</v>
+        <v>803700</v>
       </c>
       <c r="H18" s="3">
-        <v>645900</v>
+        <v>641900</v>
       </c>
       <c r="I18" s="3">
-        <v>333800</v>
+        <v>331700</v>
       </c>
       <c r="J18" s="3">
-        <v>355500</v>
+        <v>353300</v>
       </c>
       <c r="K18" s="3">
         <v>358100</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>128600</v>
+        <v>127800</v>
       </c>
       <c r="E20" s="3">
-        <v>277800</v>
+        <v>276000</v>
       </c>
       <c r="F20" s="3">
-        <v>100100</v>
+        <v>99500</v>
       </c>
       <c r="G20" s="3">
-        <v>176500</v>
+        <v>175400</v>
       </c>
       <c r="H20" s="3">
-        <v>53200</v>
+        <v>52900</v>
       </c>
       <c r="I20" s="3">
-        <v>70300</v>
+        <v>69900</v>
       </c>
       <c r="J20" s="3">
-        <v>9200</v>
+        <v>9100</v>
       </c>
       <c r="K20" s="3">
         <v>21800</v>
@@ -1229,26 +1229,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>1592600</v>
       </c>
       <c r="E21" s="3">
-        <v>1323000</v>
+        <v>1314100</v>
       </c>
       <c r="F21" s="3">
-        <v>993800</v>
+        <v>987100</v>
       </c>
       <c r="G21" s="3">
-        <v>1143700</v>
+        <v>1136200</v>
       </c>
       <c r="H21" s="3">
-        <v>831400</v>
+        <v>825800</v>
       </c>
       <c r="I21" s="3">
-        <v>527900</v>
+        <v>524300</v>
       </c>
       <c r="J21" s="3">
-        <v>520200</v>
+        <v>516400</v>
       </c>
       <c r="K21" s="3">
         <v>519600</v>
@@ -1284,16 +1284,16 @@
         <v>2000</v>
       </c>
       <c r="G22" s="3">
-        <v>9400</v>
+        <v>9300</v>
       </c>
       <c r="H22" s="3">
-        <v>12000</v>
+        <v>11900</v>
       </c>
       <c r="I22" s="3">
-        <v>22200</v>
+        <v>22100</v>
       </c>
       <c r="J22" s="3">
-        <v>11500</v>
+        <v>11400</v>
       </c>
       <c r="K22" s="3">
         <v>11800</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1388400</v>
+        <v>1379800</v>
       </c>
       <c r="E23" s="3">
-        <v>1122900</v>
+        <v>1115900</v>
       </c>
       <c r="F23" s="3">
-        <v>816500</v>
+        <v>811500</v>
       </c>
       <c r="G23" s="3">
-        <v>975800</v>
+        <v>969800</v>
       </c>
       <c r="H23" s="3">
-        <v>687100</v>
+        <v>682900</v>
       </c>
       <c r="I23" s="3">
-        <v>381900</v>
+        <v>379500</v>
       </c>
       <c r="J23" s="3">
-        <v>353200</v>
+        <v>351000</v>
       </c>
       <c r="K23" s="3">
         <v>368100</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>259400</v>
+        <v>257800</v>
       </c>
       <c r="E24" s="3">
-        <v>244500</v>
+        <v>243000</v>
       </c>
       <c r="F24" s="3">
-        <v>170000</v>
+        <v>168900</v>
       </c>
       <c r="G24" s="3">
-        <v>157100</v>
+        <v>156100</v>
       </c>
       <c r="H24" s="3">
-        <v>136700</v>
+        <v>135900</v>
       </c>
       <c r="I24" s="3">
-        <v>78800</v>
+        <v>78300</v>
       </c>
       <c r="J24" s="3">
-        <v>87000</v>
+        <v>86500</v>
       </c>
       <c r="K24" s="3">
         <v>83100</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1129000</v>
+        <v>1122000</v>
       </c>
       <c r="E26" s="3">
-        <v>878400</v>
+        <v>872900</v>
       </c>
       <c r="F26" s="3">
-        <v>646500</v>
+        <v>642500</v>
       </c>
       <c r="G26" s="3">
-        <v>818700</v>
+        <v>813700</v>
       </c>
       <c r="H26" s="3">
-        <v>550400</v>
+        <v>547000</v>
       </c>
       <c r="I26" s="3">
-        <v>303100</v>
+        <v>301300</v>
       </c>
       <c r="J26" s="3">
-        <v>266200</v>
+        <v>264500</v>
       </c>
       <c r="K26" s="3">
         <v>285000</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1128400</v>
+        <v>1121400</v>
       </c>
       <c r="E27" s="3">
-        <v>875700</v>
+        <v>870200</v>
       </c>
       <c r="F27" s="3">
-        <v>650800</v>
+        <v>646700</v>
       </c>
       <c r="G27" s="3">
-        <v>821200</v>
+        <v>816100</v>
       </c>
       <c r="H27" s="3">
-        <v>558400</v>
+        <v>555000</v>
       </c>
       <c r="I27" s="3">
-        <v>295900</v>
+        <v>294100</v>
       </c>
       <c r="J27" s="3">
-        <v>271000</v>
+        <v>269400</v>
       </c>
       <c r="K27" s="3">
         <v>281200</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-128600</v>
+        <v>-127800</v>
       </c>
       <c r="E32" s="3">
-        <v>-277800</v>
+        <v>-276000</v>
       </c>
       <c r="F32" s="3">
-        <v>-100100</v>
+        <v>-99500</v>
       </c>
       <c r="G32" s="3">
-        <v>-176500</v>
+        <v>-175400</v>
       </c>
       <c r="H32" s="3">
-        <v>-53200</v>
+        <v>-52900</v>
       </c>
       <c r="I32" s="3">
-        <v>-70300</v>
+        <v>-69900</v>
       </c>
       <c r="J32" s="3">
-        <v>-9200</v>
+        <v>-9100</v>
       </c>
       <c r="K32" s="3">
         <v>-21800</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1128400</v>
+        <v>1121400</v>
       </c>
       <c r="E33" s="3">
-        <v>875700</v>
+        <v>870200</v>
       </c>
       <c r="F33" s="3">
-        <v>650800</v>
+        <v>646700</v>
       </c>
       <c r="G33" s="3">
-        <v>821200</v>
+        <v>816100</v>
       </c>
       <c r="H33" s="3">
-        <v>558400</v>
+        <v>555000</v>
       </c>
       <c r="I33" s="3">
-        <v>295900</v>
+        <v>294100</v>
       </c>
       <c r="J33" s="3">
-        <v>271000</v>
+        <v>269400</v>
       </c>
       <c r="K33" s="3">
         <v>281200</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1128400</v>
+        <v>1121400</v>
       </c>
       <c r="E35" s="3">
-        <v>875700</v>
+        <v>870200</v>
       </c>
       <c r="F35" s="3">
-        <v>650800</v>
+        <v>646700</v>
       </c>
       <c r="G35" s="3">
-        <v>821200</v>
+        <v>816100</v>
       </c>
       <c r="H35" s="3">
-        <v>558400</v>
+        <v>555000</v>
       </c>
       <c r="I35" s="3">
-        <v>295900</v>
+        <v>294100</v>
       </c>
       <c r="J35" s="3">
-        <v>271000</v>
+        <v>269400</v>
       </c>
       <c r="K35" s="3">
         <v>281200</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3533200</v>
+        <v>3511300</v>
       </c>
       <c r="E41" s="3">
-        <v>3049900</v>
+        <v>3031000</v>
       </c>
       <c r="F41" s="3">
-        <v>2265700</v>
+        <v>2251700</v>
       </c>
       <c r="G41" s="3">
-        <v>1667600</v>
+        <v>1657300</v>
       </c>
       <c r="H41" s="3">
-        <v>913900</v>
+        <v>908200</v>
       </c>
       <c r="I41" s="3">
-        <v>1326300</v>
+        <v>1318100</v>
       </c>
       <c r="J41" s="3">
-        <v>1386600</v>
+        <v>1378000</v>
       </c>
       <c r="K41" s="3">
         <v>567500</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>275700</v>
+        <v>274000</v>
       </c>
       <c r="E42" s="3">
-        <v>221900</v>
+        <v>220500</v>
       </c>
       <c r="F42" s="3">
-        <v>748200</v>
+        <v>743500</v>
       </c>
       <c r="G42" s="3">
-        <v>1018800</v>
+        <v>1012500</v>
       </c>
       <c r="H42" s="3">
-        <v>424400</v>
+        <v>421800</v>
       </c>
       <c r="I42" s="3">
-        <v>322700</v>
+        <v>320700</v>
       </c>
       <c r="J42" s="3">
-        <v>34200</v>
+        <v>34000</v>
       </c>
       <c r="K42" s="3">
         <v>92800</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>505400</v>
+        <v>502300</v>
       </c>
       <c r="E43" s="3">
-        <v>489200</v>
+        <v>486200</v>
       </c>
       <c r="F43" s="3">
-        <v>476000</v>
+        <v>473100</v>
       </c>
       <c r="G43" s="3">
-        <v>414500</v>
+        <v>411900</v>
       </c>
       <c r="H43" s="3">
-        <v>632200</v>
+        <v>628300</v>
       </c>
       <c r="I43" s="3">
-        <v>1334300</v>
+        <v>1326000</v>
       </c>
       <c r="J43" s="3">
-        <v>1180000</v>
+        <v>1172700</v>
       </c>
       <c r="K43" s="3">
         <v>627400</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>784700</v>
+        <v>779900</v>
       </c>
       <c r="E44" s="3">
-        <v>766800</v>
+        <v>762100</v>
       </c>
       <c r="F44" s="3">
-        <v>954400</v>
+        <v>948500</v>
       </c>
       <c r="G44" s="3">
-        <v>1062500</v>
+        <v>1055900</v>
       </c>
       <c r="H44" s="3">
-        <v>1071600</v>
+        <v>1065000</v>
       </c>
       <c r="I44" s="3">
-        <v>746300</v>
+        <v>741700</v>
       </c>
       <c r="J44" s="3">
-        <v>967600</v>
+        <v>961600</v>
       </c>
       <c r="K44" s="3">
         <v>683300</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>122700</v>
+        <v>121900</v>
       </c>
       <c r="E45" s="3">
-        <v>161900</v>
+        <v>160900</v>
       </c>
       <c r="F45" s="3">
-        <v>121500</v>
+        <v>120700</v>
       </c>
       <c r="G45" s="3">
-        <v>170300</v>
+        <v>169200</v>
       </c>
       <c r="H45" s="3">
-        <v>159200</v>
+        <v>158300</v>
       </c>
       <c r="I45" s="3">
-        <v>69200</v>
+        <v>68800</v>
       </c>
       <c r="J45" s="3">
-        <v>34500</v>
+        <v>34300</v>
       </c>
       <c r="K45" s="3">
         <v>42400</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5221700</v>
+        <v>5189400</v>
       </c>
       <c r="E46" s="3">
-        <v>4689800</v>
+        <v>4660700</v>
       </c>
       <c r="F46" s="3">
-        <v>4565700</v>
+        <v>4537400</v>
       </c>
       <c r="G46" s="3">
-        <v>4333700</v>
+        <v>4306900</v>
       </c>
       <c r="H46" s="3">
-        <v>3201400</v>
+        <v>3181600</v>
       </c>
       <c r="I46" s="3">
-        <v>3798800</v>
+        <v>3775300</v>
       </c>
       <c r="J46" s="3">
-        <v>3602900</v>
+        <v>3580600</v>
       </c>
       <c r="K46" s="3">
         <v>2013300</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>705100</v>
+        <v>700700</v>
       </c>
       <c r="E47" s="3">
-        <v>670500</v>
+        <v>666400</v>
       </c>
       <c r="F47" s="3">
-        <v>689500</v>
+        <v>685200</v>
       </c>
       <c r="G47" s="3">
-        <v>668800</v>
+        <v>664700</v>
       </c>
       <c r="H47" s="3">
-        <v>725400</v>
+        <v>720900</v>
       </c>
       <c r="I47" s="3">
-        <v>297200</v>
+        <v>295400</v>
       </c>
       <c r="J47" s="3">
-        <v>83400</v>
+        <v>82900</v>
       </c>
       <c r="K47" s="3">
         <v>138700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2424000</v>
+        <v>2409000</v>
       </c>
       <c r="E48" s="3">
-        <v>2379700</v>
+        <v>2364900</v>
       </c>
       <c r="F48" s="3">
-        <v>2158300</v>
+        <v>2144900</v>
       </c>
       <c r="G48" s="3">
-        <v>2108300</v>
+        <v>2095200</v>
       </c>
       <c r="H48" s="3">
-        <v>1803400</v>
+        <v>1792300</v>
       </c>
       <c r="I48" s="3">
-        <v>1186000</v>
+        <v>1178700</v>
       </c>
       <c r="J48" s="3">
-        <v>926000</v>
+        <v>920300</v>
       </c>
       <c r="K48" s="3">
         <v>616900</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>151300</v>
+        <v>150300</v>
       </c>
       <c r="E49" s="3">
-        <v>151800</v>
+        <v>150800</v>
       </c>
       <c r="F49" s="3">
-        <v>126500</v>
+        <v>125700</v>
       </c>
       <c r="G49" s="3">
-        <v>128800</v>
+        <v>128000</v>
       </c>
       <c r="H49" s="3">
-        <v>79800</v>
+        <v>79300</v>
       </c>
       <c r="I49" s="3">
-        <v>100100</v>
+        <v>99500</v>
       </c>
       <c r="J49" s="3">
-        <v>106800</v>
+        <v>106100</v>
       </c>
       <c r="K49" s="3">
         <v>150800</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1552300</v>
+        <v>1542700</v>
       </c>
       <c r="E52" s="3">
-        <v>1210700</v>
+        <v>1203200</v>
       </c>
       <c r="F52" s="3">
-        <v>1119200</v>
+        <v>1112300</v>
       </c>
       <c r="G52" s="3">
-        <v>954400</v>
+        <v>948500</v>
       </c>
       <c r="H52" s="3">
-        <v>944000</v>
+        <v>938200</v>
       </c>
       <c r="I52" s="3">
-        <v>673900</v>
+        <v>669700</v>
       </c>
       <c r="J52" s="3">
-        <v>561300</v>
+        <v>557800</v>
       </c>
       <c r="K52" s="3">
         <v>545400</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>10054300</v>
+        <v>9992100</v>
       </c>
       <c r="E54" s="3">
-        <v>9102400</v>
+        <v>9046100</v>
       </c>
       <c r="F54" s="3">
-        <v>8659200</v>
+        <v>8605600</v>
       </c>
       <c r="G54" s="3">
-        <v>8194000</v>
+        <v>8143300</v>
       </c>
       <c r="H54" s="3">
-        <v>6754000</v>
+        <v>6712200</v>
       </c>
       <c r="I54" s="3">
-        <v>6056100</v>
+        <v>6018600</v>
       </c>
       <c r="J54" s="3">
-        <v>5280400</v>
+        <v>5247700</v>
       </c>
       <c r="K54" s="3">
         <v>3465000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2399400</v>
+        <v>2384600</v>
       </c>
       <c r="E57" s="3">
-        <v>2087800</v>
+        <v>2074900</v>
       </c>
       <c r="F57" s="3">
-        <v>1827400</v>
+        <v>1816100</v>
       </c>
       <c r="G57" s="3">
-        <v>2111900</v>
+        <v>2098800</v>
       </c>
       <c r="H57" s="3">
-        <v>1917400</v>
+        <v>1905500</v>
       </c>
       <c r="I57" s="3">
-        <v>1616800</v>
+        <v>1606800</v>
       </c>
       <c r="J57" s="3">
-        <v>1591100</v>
+        <v>1581300</v>
       </c>
       <c r="K57" s="3">
         <v>1150700</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>198200</v>
+        <v>197000</v>
       </c>
       <c r="E58" s="3">
-        <v>373600</v>
+        <v>371300</v>
       </c>
       <c r="F58" s="3">
-        <v>274600</v>
+        <v>272900</v>
       </c>
       <c r="G58" s="3">
-        <v>145100</v>
+        <v>144200</v>
       </c>
       <c r="H58" s="3">
-        <v>152000</v>
+        <v>151100</v>
       </c>
       <c r="I58" s="3">
-        <v>923000</v>
+        <v>917300</v>
       </c>
       <c r="J58" s="3">
-        <v>231800</v>
+        <v>230400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1659800</v>
+        <v>1649500</v>
       </c>
       <c r="E59" s="3">
-        <v>1504300</v>
+        <v>1495000</v>
       </c>
       <c r="F59" s="3">
-        <v>1480700</v>
+        <v>1471500</v>
       </c>
       <c r="G59" s="3">
-        <v>1436700</v>
+        <v>1427800</v>
       </c>
       <c r="H59" s="3">
-        <v>1256700</v>
+        <v>1248900</v>
       </c>
       <c r="I59" s="3">
-        <v>1067200</v>
+        <v>1060600</v>
       </c>
       <c r="J59" s="3">
-        <v>854300</v>
+        <v>849000</v>
       </c>
       <c r="K59" s="3">
         <v>863000</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4257400</v>
+        <v>4231000</v>
       </c>
       <c r="E60" s="3">
-        <v>3965700</v>
+        <v>3941200</v>
       </c>
       <c r="F60" s="3">
-        <v>3582700</v>
+        <v>3560500</v>
       </c>
       <c r="G60" s="3">
-        <v>3693600</v>
+        <v>3670800</v>
       </c>
       <c r="H60" s="3">
-        <v>3326100</v>
+        <v>3305600</v>
       </c>
       <c r="I60" s="3">
-        <v>3607000</v>
+        <v>3584700</v>
       </c>
       <c r="J60" s="3">
-        <v>2677200</v>
+        <v>2660600</v>
       </c>
       <c r="K60" s="3">
         <v>2013700</v>
@@ -2853,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>569300</v>
+        <v>565800</v>
       </c>
       <c r="K61" s="3">
         <v>605000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>436300</v>
+        <v>433600</v>
       </c>
       <c r="E62" s="3">
-        <v>399900</v>
+        <v>397400</v>
       </c>
       <c r="F62" s="3">
-        <v>373700</v>
+        <v>371400</v>
       </c>
       <c r="G62" s="3">
-        <v>415100</v>
+        <v>412600</v>
       </c>
       <c r="H62" s="3">
-        <v>325700</v>
+        <v>323700</v>
       </c>
       <c r="I62" s="3">
-        <v>56400</v>
+        <v>56100</v>
       </c>
       <c r="J62" s="3">
-        <v>52800</v>
+        <v>52500</v>
       </c>
       <c r="K62" s="3">
         <v>48000</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4915900</v>
+        <v>4885500</v>
       </c>
       <c r="E66" s="3">
-        <v>4549200</v>
+        <v>4521100</v>
       </c>
       <c r="F66" s="3">
-        <v>4122600</v>
+        <v>4097100</v>
       </c>
       <c r="G66" s="3">
-        <v>4232200</v>
+        <v>4206000</v>
       </c>
       <c r="H66" s="3">
-        <v>3719600</v>
+        <v>3696500</v>
       </c>
       <c r="I66" s="3">
-        <v>3656300</v>
+        <v>3633700</v>
       </c>
       <c r="J66" s="3">
-        <v>3293100</v>
+        <v>3272800</v>
       </c>
       <c r="K66" s="3">
         <v>2673500</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>5121100</v>
+        <v>5089400</v>
       </c>
       <c r="E72" s="3">
-        <v>3992700</v>
+        <v>3968000</v>
       </c>
       <c r="F72" s="3">
-        <v>3117000</v>
+        <v>3097800</v>
       </c>
       <c r="G72" s="3">
-        <v>2466300</v>
+        <v>2451000</v>
       </c>
       <c r="H72" s="3">
-        <v>1657700</v>
+        <v>1647500</v>
       </c>
       <c r="I72" s="3">
-        <v>1099300</v>
+        <v>1092500</v>
       </c>
       <c r="J72" s="3">
-        <v>778900</v>
+        <v>774100</v>
       </c>
       <c r="K72" s="3">
         <v>504400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5138400</v>
+        <v>5106600</v>
       </c>
       <c r="E76" s="3">
-        <v>4553200</v>
+        <v>4525000</v>
       </c>
       <c r="F76" s="3">
-        <v>4536600</v>
+        <v>4508600</v>
       </c>
       <c r="G76" s="3">
-        <v>3961800</v>
+        <v>3937200</v>
       </c>
       <c r="H76" s="3">
-        <v>3034400</v>
+        <v>3015600</v>
       </c>
       <c r="I76" s="3">
-        <v>2399700</v>
+        <v>2384900</v>
       </c>
       <c r="J76" s="3">
-        <v>1987200</v>
+        <v>1974900</v>
       </c>
       <c r="K76" s="3">
         <v>791500</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1128400</v>
+        <v>1121400</v>
       </c>
       <c r="E81" s="3">
-        <v>875700</v>
+        <v>870200</v>
       </c>
       <c r="F81" s="3">
-        <v>650800</v>
+        <v>646700</v>
       </c>
       <c r="G81" s="3">
-        <v>821200</v>
+        <v>816100</v>
       </c>
       <c r="H81" s="3">
-        <v>558400</v>
+        <v>555000</v>
       </c>
       <c r="I81" s="3">
-        <v>295900</v>
+        <v>294100</v>
       </c>
       <c r="J81" s="3">
-        <v>271000</v>
+        <v>269400</v>
       </c>
       <c r="K81" s="3">
         <v>281200</v>
@@ -3693,26 +3693,26 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>210100</v>
       </c>
       <c r="E83" s="3">
-        <v>196500</v>
+        <v>195300</v>
       </c>
       <c r="F83" s="3">
-        <v>175100</v>
+        <v>174000</v>
       </c>
       <c r="G83" s="3">
-        <v>158400</v>
+        <v>157400</v>
       </c>
       <c r="H83" s="3">
-        <v>132100</v>
+        <v>131300</v>
       </c>
       <c r="I83" s="3">
-        <v>123700</v>
+        <v>122900</v>
       </c>
       <c r="J83" s="3">
-        <v>155300</v>
+        <v>154400</v>
       </c>
       <c r="K83" s="3">
         <v>139800</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2003900</v>
+        <v>1991500</v>
       </c>
       <c r="E89" s="3">
-        <v>1462400</v>
+        <v>1453400</v>
       </c>
       <c r="F89" s="3">
-        <v>937600</v>
+        <v>931800</v>
       </c>
       <c r="G89" s="3">
-        <v>1643300</v>
+        <v>1633100</v>
       </c>
       <c r="H89" s="3">
-        <v>1708600</v>
+        <v>1698000</v>
       </c>
       <c r="I89" s="3">
-        <v>798800</v>
+        <v>793800</v>
       </c>
       <c r="J89" s="3">
-        <v>136400</v>
+        <v>135600</v>
       </c>
       <c r="K89" s="3">
         <v>391000</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-727200</v>
+        <v>-722700</v>
       </c>
       <c r="E91" s="3">
-        <v>-431300</v>
+        <v>-428700</v>
       </c>
       <c r="F91" s="3">
-        <v>-497500</v>
+        <v>-494400</v>
       </c>
       <c r="G91" s="3">
-        <v>-315800</v>
+        <v>-313900</v>
       </c>
       <c r="H91" s="3">
-        <v>-594700</v>
+        <v>-591000</v>
       </c>
       <c r="I91" s="3">
-        <v>-499600</v>
+        <v>-496500</v>
       </c>
       <c r="J91" s="3">
-        <v>-344000</v>
+        <v>-341900</v>
       </c>
       <c r="K91" s="3">
         <v>-300000</v>
@@ -4162,26 +4162,26 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>-713000</v>
       </c>
       <c r="E94" s="3">
-        <v>145900</v>
+        <v>145000</v>
       </c>
       <c r="F94" s="3">
-        <v>-323400</v>
+        <v>-321400</v>
       </c>
       <c r="G94" s="3">
-        <v>-930700</v>
+        <v>-925000</v>
       </c>
       <c r="H94" s="3">
-        <v>-1145600</v>
+        <v>-1138500</v>
       </c>
       <c r="I94" s="3">
-        <v>-930600</v>
+        <v>-924800</v>
       </c>
       <c r="J94" s="3">
-        <v>-282600</v>
+        <v>-280800</v>
       </c>
       <c r="K94" s="3">
         <v>-230500</v>
@@ -4406,26 +4406,26 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>-849100</v>
       </c>
       <c r="E100" s="3">
-        <v>-774800</v>
+        <v>-770000</v>
       </c>
       <c r="F100" s="3">
-        <v>-8200</v>
+        <v>-8100</v>
       </c>
       <c r="G100" s="3">
         <v>-2900</v>
       </c>
       <c r="H100" s="3">
-        <v>-869800</v>
+        <v>-864400</v>
       </c>
       <c r="I100" s="3">
-        <v>81600</v>
+        <v>81100</v>
       </c>
       <c r="J100" s="3">
-        <v>996700</v>
+        <v>990600</v>
       </c>
       <c r="K100" s="3">
         <v>-54300</v>
@@ -4451,11 +4451,11 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>11900</v>
       </c>
       <c r="E101" s="3">
-        <v>-8800</v>
+        <v>-8700</v>
       </c>
       <c r="F101" s="3">
         <v>100</v>
@@ -4464,10 +4464,10 @@
         <v>-1700</v>
       </c>
       <c r="H101" s="3">
-        <v>-15600</v>
+        <v>-15500</v>
       </c>
       <c r="I101" s="3">
-        <v>24700</v>
+        <v>24500</v>
       </c>
       <c r="J101" s="3">
         <v>-800</v>
@@ -4496,26 +4496,26 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>8</v>
+      <c r="D102" s="3">
+        <v>441300</v>
       </c>
       <c r="E102" s="3">
-        <v>824700</v>
+        <v>819600</v>
       </c>
       <c r="F102" s="3">
-        <v>606100</v>
+        <v>602400</v>
       </c>
       <c r="G102" s="3">
-        <v>707900</v>
+        <v>703500</v>
       </c>
       <c r="H102" s="3">
-        <v>-322400</v>
+        <v>-320400</v>
       </c>
       <c r="I102" s="3">
-        <v>-25500</v>
+        <v>-25400</v>
       </c>
       <c r="J102" s="3">
-        <v>849700</v>
+        <v>844500</v>
       </c>
       <c r="K102" s="3">
         <v>108400</v>

--- a/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>15592200</v>
+        <v>15910400</v>
       </c>
       <c r="E8" s="3">
-        <v>14251500</v>
+        <v>14542400</v>
       </c>
       <c r="F8" s="3">
-        <v>16173000</v>
+        <v>16503100</v>
       </c>
       <c r="G8" s="3">
-        <v>14072800</v>
+        <v>14360000</v>
       </c>
       <c r="H8" s="3">
-        <v>12848100</v>
+        <v>13110400</v>
       </c>
       <c r="I8" s="3">
-        <v>11677800</v>
+        <v>11916200</v>
       </c>
       <c r="J8" s="3">
-        <v>10073600</v>
+        <v>10279200</v>
       </c>
       <c r="K8" s="3">
         <v>7814100</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>12038600</v>
+        <v>12284300</v>
       </c>
       <c r="E9" s="3">
-        <v>11265100</v>
+        <v>11495000</v>
       </c>
       <c r="F9" s="3">
-        <v>12980600</v>
+        <v>13245500</v>
       </c>
       <c r="G9" s="3">
-        <v>11132000</v>
+        <v>11359200</v>
       </c>
       <c r="H9" s="3">
-        <v>9990900</v>
+        <v>10194900</v>
       </c>
       <c r="I9" s="3">
-        <v>9319600</v>
+        <v>9509800</v>
       </c>
       <c r="J9" s="3">
-        <v>7822400</v>
+        <v>7982100</v>
       </c>
       <c r="K9" s="3">
         <v>5936700</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3553600</v>
+        <v>3626100</v>
       </c>
       <c r="E10" s="3">
-        <v>2986500</v>
+        <v>3047400</v>
       </c>
       <c r="F10" s="3">
-        <v>3192400</v>
+        <v>3257600</v>
       </c>
       <c r="G10" s="3">
-        <v>2940800</v>
+        <v>3000800</v>
       </c>
       <c r="H10" s="3">
-        <v>2857200</v>
+        <v>2915500</v>
       </c>
       <c r="I10" s="3">
-        <v>2358200</v>
+        <v>2406400</v>
       </c>
       <c r="J10" s="3">
-        <v>2251200</v>
+        <v>2297100</v>
       </c>
       <c r="K10" s="3">
         <v>1877400</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>24200</v>
+        <v>24700</v>
       </c>
       <c r="E14" s="3">
-        <v>46000</v>
+        <v>47000</v>
       </c>
       <c r="F14" s="3">
-        <v>57300</v>
+        <v>58500</v>
       </c>
       <c r="G14" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="H14" s="3">
-        <v>56100</v>
+        <v>57200</v>
       </c>
       <c r="I14" s="3">
         <v>2800</v>
       </c>
       <c r="J14" s="3">
-        <v>18400</v>
+        <v>18800</v>
       </c>
       <c r="K14" s="3">
         <v>15800</v>
@@ -1027,13 +1027,13 @@
         <v>8</v>
       </c>
       <c r="H15" s="3">
-        <v>114700</v>
+        <v>117100</v>
       </c>
       <c r="I15" s="3">
-        <v>106400</v>
+        <v>108600</v>
       </c>
       <c r="J15" s="3">
-        <v>99600</v>
+        <v>101600</v>
       </c>
       <c r="K15" s="3">
         <v>84400</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14337000</v>
+        <v>14629600</v>
       </c>
       <c r="E17" s="3">
-        <v>13408300</v>
+        <v>13682000</v>
       </c>
       <c r="F17" s="3">
-        <v>15459000</v>
+        <v>15774500</v>
       </c>
       <c r="G17" s="3">
-        <v>13269100</v>
+        <v>13539900</v>
       </c>
       <c r="H17" s="3">
-        <v>12206200</v>
+        <v>12455400</v>
       </c>
       <c r="I17" s="3">
-        <v>11346100</v>
+        <v>11577700</v>
       </c>
       <c r="J17" s="3">
-        <v>9720200</v>
+        <v>9918600</v>
       </c>
       <c r="K17" s="3">
         <v>7456100</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1255200</v>
+        <v>1280800</v>
       </c>
       <c r="E18" s="3">
-        <v>843300</v>
+        <v>860500</v>
       </c>
       <c r="F18" s="3">
-        <v>714000</v>
+        <v>728500</v>
       </c>
       <c r="G18" s="3">
-        <v>803700</v>
+        <v>820100</v>
       </c>
       <c r="H18" s="3">
-        <v>641900</v>
+        <v>655000</v>
       </c>
       <c r="I18" s="3">
-        <v>331700</v>
+        <v>338500</v>
       </c>
       <c r="J18" s="3">
-        <v>353300</v>
+        <v>360500</v>
       </c>
       <c r="K18" s="3">
         <v>358100</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>127800</v>
+        <v>130400</v>
       </c>
       <c r="E20" s="3">
-        <v>276000</v>
+        <v>281700</v>
       </c>
       <c r="F20" s="3">
-        <v>99500</v>
+        <v>101500</v>
       </c>
       <c r="G20" s="3">
-        <v>175400</v>
+        <v>179000</v>
       </c>
       <c r="H20" s="3">
-        <v>52900</v>
+        <v>54000</v>
       </c>
       <c r="I20" s="3">
-        <v>69900</v>
+        <v>71300</v>
       </c>
       <c r="J20" s="3">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="K20" s="3">
         <v>21800</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1592600</v>
+        <v>1624800</v>
       </c>
       <c r="E21" s="3">
-        <v>1314100</v>
+        <v>1340700</v>
       </c>
       <c r="F21" s="3">
-        <v>987100</v>
+        <v>1007000</v>
       </c>
       <c r="G21" s="3">
-        <v>1136200</v>
+        <v>1159200</v>
       </c>
       <c r="H21" s="3">
-        <v>825800</v>
+        <v>842500</v>
       </c>
       <c r="I21" s="3">
-        <v>524300</v>
+        <v>534800</v>
       </c>
       <c r="J21" s="3">
-        <v>516400</v>
+        <v>526800</v>
       </c>
       <c r="K21" s="3">
         <v>519600</v>
@@ -1284,16 +1284,16 @@
         <v>2000</v>
       </c>
       <c r="G22" s="3">
-        <v>9300</v>
+        <v>9500</v>
       </c>
       <c r="H22" s="3">
-        <v>11900</v>
+        <v>12100</v>
       </c>
       <c r="I22" s="3">
-        <v>22100</v>
+        <v>22500</v>
       </c>
       <c r="J22" s="3">
-        <v>11400</v>
+        <v>11600</v>
       </c>
       <c r="K22" s="3">
         <v>11800</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1379800</v>
+        <v>1408000</v>
       </c>
       <c r="E23" s="3">
-        <v>1115900</v>
+        <v>1138700</v>
       </c>
       <c r="F23" s="3">
-        <v>811500</v>
+        <v>828000</v>
       </c>
       <c r="G23" s="3">
-        <v>969800</v>
+        <v>989600</v>
       </c>
       <c r="H23" s="3">
-        <v>682900</v>
+        <v>696800</v>
       </c>
       <c r="I23" s="3">
-        <v>379500</v>
+        <v>387300</v>
       </c>
       <c r="J23" s="3">
-        <v>351000</v>
+        <v>358200</v>
       </c>
       <c r="K23" s="3">
         <v>368100</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>257800</v>
+        <v>263100</v>
       </c>
       <c r="E24" s="3">
-        <v>243000</v>
+        <v>248000</v>
       </c>
       <c r="F24" s="3">
-        <v>168900</v>
+        <v>172400</v>
       </c>
       <c r="G24" s="3">
-        <v>156100</v>
+        <v>159300</v>
       </c>
       <c r="H24" s="3">
-        <v>135900</v>
+        <v>138700</v>
       </c>
       <c r="I24" s="3">
-        <v>78300</v>
+        <v>79900</v>
       </c>
       <c r="J24" s="3">
-        <v>86500</v>
+        <v>88300</v>
       </c>
       <c r="K24" s="3">
         <v>83100</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1122000</v>
+        <v>1144900</v>
       </c>
       <c r="E26" s="3">
-        <v>872900</v>
+        <v>890800</v>
       </c>
       <c r="F26" s="3">
-        <v>642500</v>
+        <v>655600</v>
       </c>
       <c r="G26" s="3">
-        <v>813700</v>
+        <v>830300</v>
       </c>
       <c r="H26" s="3">
-        <v>547000</v>
+        <v>558200</v>
       </c>
       <c r="I26" s="3">
-        <v>301300</v>
+        <v>307400</v>
       </c>
       <c r="J26" s="3">
-        <v>264500</v>
+        <v>269900</v>
       </c>
       <c r="K26" s="3">
         <v>285000</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1121400</v>
+        <v>1144300</v>
       </c>
       <c r="E27" s="3">
-        <v>870200</v>
+        <v>888000</v>
       </c>
       <c r="F27" s="3">
-        <v>646700</v>
+        <v>659900</v>
       </c>
       <c r="G27" s="3">
-        <v>816100</v>
+        <v>832800</v>
       </c>
       <c r="H27" s="3">
-        <v>555000</v>
+        <v>566300</v>
       </c>
       <c r="I27" s="3">
-        <v>294100</v>
+        <v>300100</v>
       </c>
       <c r="J27" s="3">
-        <v>269400</v>
+        <v>274900</v>
       </c>
       <c r="K27" s="3">
         <v>281200</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-127800</v>
+        <v>-130400</v>
       </c>
       <c r="E32" s="3">
-        <v>-276000</v>
+        <v>-281700</v>
       </c>
       <c r="F32" s="3">
-        <v>-99500</v>
+        <v>-101500</v>
       </c>
       <c r="G32" s="3">
-        <v>-175400</v>
+        <v>-179000</v>
       </c>
       <c r="H32" s="3">
-        <v>-52900</v>
+        <v>-54000</v>
       </c>
       <c r="I32" s="3">
-        <v>-69900</v>
+        <v>-71300</v>
       </c>
       <c r="J32" s="3">
-        <v>-9100</v>
+        <v>-9300</v>
       </c>
       <c r="K32" s="3">
         <v>-21800</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1121400</v>
+        <v>1144300</v>
       </c>
       <c r="E33" s="3">
-        <v>870200</v>
+        <v>888000</v>
       </c>
       <c r="F33" s="3">
-        <v>646700</v>
+        <v>659900</v>
       </c>
       <c r="G33" s="3">
-        <v>816100</v>
+        <v>832800</v>
       </c>
       <c r="H33" s="3">
-        <v>555000</v>
+        <v>566300</v>
       </c>
       <c r="I33" s="3">
-        <v>294100</v>
+        <v>300100</v>
       </c>
       <c r="J33" s="3">
-        <v>269400</v>
+        <v>274900</v>
       </c>
       <c r="K33" s="3">
         <v>281200</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1121400</v>
+        <v>1144300</v>
       </c>
       <c r="E35" s="3">
-        <v>870200</v>
+        <v>888000</v>
       </c>
       <c r="F35" s="3">
-        <v>646700</v>
+        <v>659900</v>
       </c>
       <c r="G35" s="3">
-        <v>816100</v>
+        <v>832800</v>
       </c>
       <c r="H35" s="3">
-        <v>555000</v>
+        <v>566300</v>
       </c>
       <c r="I35" s="3">
-        <v>294100</v>
+        <v>300100</v>
       </c>
       <c r="J35" s="3">
-        <v>269400</v>
+        <v>274900</v>
       </c>
       <c r="K35" s="3">
         <v>281200</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3511300</v>
+        <v>3583000</v>
       </c>
       <c r="E41" s="3">
-        <v>3031000</v>
+        <v>3092900</v>
       </c>
       <c r="F41" s="3">
-        <v>2251700</v>
+        <v>2297600</v>
       </c>
       <c r="G41" s="3">
-        <v>1657300</v>
+        <v>1691100</v>
       </c>
       <c r="H41" s="3">
-        <v>908200</v>
+        <v>926800</v>
       </c>
       <c r="I41" s="3">
-        <v>1318100</v>
+        <v>1345000</v>
       </c>
       <c r="J41" s="3">
-        <v>1378000</v>
+        <v>1406100</v>
       </c>
       <c r="K41" s="3">
         <v>567500</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>274000</v>
+        <v>279600</v>
       </c>
       <c r="E42" s="3">
-        <v>220500</v>
+        <v>225000</v>
       </c>
       <c r="F42" s="3">
-        <v>743500</v>
+        <v>758700</v>
       </c>
       <c r="G42" s="3">
-        <v>1012500</v>
+        <v>1033200</v>
       </c>
       <c r="H42" s="3">
-        <v>421800</v>
+        <v>430400</v>
       </c>
       <c r="I42" s="3">
-        <v>320700</v>
+        <v>327200</v>
       </c>
       <c r="J42" s="3">
-        <v>34000</v>
+        <v>34700</v>
       </c>
       <c r="K42" s="3">
         <v>92800</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>502300</v>
+        <v>512500</v>
       </c>
       <c r="E43" s="3">
-        <v>486200</v>
+        <v>496100</v>
       </c>
       <c r="F43" s="3">
-        <v>473100</v>
+        <v>482700</v>
       </c>
       <c r="G43" s="3">
-        <v>411900</v>
+        <v>420400</v>
       </c>
       <c r="H43" s="3">
-        <v>628300</v>
+        <v>641100</v>
       </c>
       <c r="I43" s="3">
-        <v>1326000</v>
+        <v>1353100</v>
       </c>
       <c r="J43" s="3">
-        <v>1172700</v>
+        <v>1196600</v>
       </c>
       <c r="K43" s="3">
         <v>627400</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>779900</v>
+        <v>795800</v>
       </c>
       <c r="E44" s="3">
-        <v>762100</v>
+        <v>777600</v>
       </c>
       <c r="F44" s="3">
-        <v>948500</v>
+        <v>967800</v>
       </c>
       <c r="G44" s="3">
-        <v>1055900</v>
+        <v>1077400</v>
       </c>
       <c r="H44" s="3">
-        <v>1065000</v>
+        <v>1086700</v>
       </c>
       <c r="I44" s="3">
-        <v>741700</v>
+        <v>756800</v>
       </c>
       <c r="J44" s="3">
-        <v>961600</v>
+        <v>981300</v>
       </c>
       <c r="K44" s="3">
         <v>683300</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>121900</v>
+        <v>124400</v>
       </c>
       <c r="E45" s="3">
-        <v>160900</v>
+        <v>164200</v>
       </c>
       <c r="F45" s="3">
-        <v>120700</v>
+        <v>123200</v>
       </c>
       <c r="G45" s="3">
-        <v>169200</v>
+        <v>172700</v>
       </c>
       <c r="H45" s="3">
-        <v>158300</v>
+        <v>161500</v>
       </c>
       <c r="I45" s="3">
-        <v>68800</v>
+        <v>70200</v>
       </c>
       <c r="J45" s="3">
-        <v>34300</v>
+        <v>35000</v>
       </c>
       <c r="K45" s="3">
         <v>42400</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5189400</v>
+        <v>5295300</v>
       </c>
       <c r="E46" s="3">
-        <v>4660700</v>
+        <v>4755900</v>
       </c>
       <c r="F46" s="3">
-        <v>4537400</v>
+        <v>4630100</v>
       </c>
       <c r="G46" s="3">
-        <v>4306900</v>
+        <v>4394800</v>
       </c>
       <c r="H46" s="3">
-        <v>3181600</v>
+        <v>3246500</v>
       </c>
       <c r="I46" s="3">
-        <v>3775300</v>
+        <v>3852400</v>
       </c>
       <c r="J46" s="3">
-        <v>3580600</v>
+        <v>3653700</v>
       </c>
       <c r="K46" s="3">
         <v>2013300</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>700700</v>
+        <v>715000</v>
       </c>
       <c r="E47" s="3">
-        <v>666400</v>
+        <v>680000</v>
       </c>
       <c r="F47" s="3">
-        <v>685200</v>
+        <v>699200</v>
       </c>
       <c r="G47" s="3">
-        <v>664700</v>
+        <v>678200</v>
       </c>
       <c r="H47" s="3">
-        <v>720900</v>
+        <v>735600</v>
       </c>
       <c r="I47" s="3">
-        <v>295400</v>
+        <v>301400</v>
       </c>
       <c r="J47" s="3">
-        <v>82900</v>
+        <v>84600</v>
       </c>
       <c r="K47" s="3">
         <v>138700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2409000</v>
+        <v>2458100</v>
       </c>
       <c r="E48" s="3">
-        <v>2364900</v>
+        <v>2413200</v>
       </c>
       <c r="F48" s="3">
-        <v>2144900</v>
+        <v>2188700</v>
       </c>
       <c r="G48" s="3">
-        <v>2095200</v>
+        <v>2138000</v>
       </c>
       <c r="H48" s="3">
-        <v>1792300</v>
+        <v>1828800</v>
       </c>
       <c r="I48" s="3">
-        <v>1178700</v>
+        <v>1202800</v>
       </c>
       <c r="J48" s="3">
-        <v>920300</v>
+        <v>939000</v>
       </c>
       <c r="K48" s="3">
         <v>616900</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>150300</v>
+        <v>153400</v>
       </c>
       <c r="E49" s="3">
-        <v>150800</v>
+        <v>153900</v>
       </c>
       <c r="F49" s="3">
-        <v>125700</v>
+        <v>128300</v>
       </c>
       <c r="G49" s="3">
-        <v>128000</v>
+        <v>130600</v>
       </c>
       <c r="H49" s="3">
-        <v>79300</v>
+        <v>80900</v>
       </c>
       <c r="I49" s="3">
-        <v>99500</v>
+        <v>101500</v>
       </c>
       <c r="J49" s="3">
-        <v>106100</v>
+        <v>108300</v>
       </c>
       <c r="K49" s="3">
         <v>150800</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1542700</v>
+        <v>1574200</v>
       </c>
       <c r="E52" s="3">
-        <v>1203200</v>
+        <v>1227800</v>
       </c>
       <c r="F52" s="3">
-        <v>1112300</v>
+        <v>1135000</v>
       </c>
       <c r="G52" s="3">
-        <v>948500</v>
+        <v>967800</v>
       </c>
       <c r="H52" s="3">
-        <v>938200</v>
+        <v>957300</v>
       </c>
       <c r="I52" s="3">
-        <v>669700</v>
+        <v>683400</v>
       </c>
       <c r="J52" s="3">
-        <v>557800</v>
+        <v>569200</v>
       </c>
       <c r="K52" s="3">
         <v>545400</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9992100</v>
+        <v>10196000</v>
       </c>
       <c r="E54" s="3">
-        <v>9046100</v>
+        <v>9230700</v>
       </c>
       <c r="F54" s="3">
-        <v>8605600</v>
+        <v>8781300</v>
       </c>
       <c r="G54" s="3">
-        <v>8143300</v>
+        <v>8309500</v>
       </c>
       <c r="H54" s="3">
-        <v>6712200</v>
+        <v>6849200</v>
       </c>
       <c r="I54" s="3">
-        <v>6018600</v>
+        <v>6141500</v>
       </c>
       <c r="J54" s="3">
-        <v>5247700</v>
+        <v>5354800</v>
       </c>
       <c r="K54" s="3">
         <v>3465000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2384600</v>
+        <v>2433200</v>
       </c>
       <c r="E57" s="3">
-        <v>2074900</v>
+        <v>2117300</v>
       </c>
       <c r="F57" s="3">
-        <v>1816100</v>
+        <v>1853200</v>
       </c>
       <c r="G57" s="3">
-        <v>2098800</v>
+        <v>2141700</v>
       </c>
       <c r="H57" s="3">
-        <v>1905500</v>
+        <v>1944400</v>
       </c>
       <c r="I57" s="3">
-        <v>1606800</v>
+        <v>1639600</v>
       </c>
       <c r="J57" s="3">
-        <v>1581300</v>
+        <v>1613500</v>
       </c>
       <c r="K57" s="3">
         <v>1150700</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>197000</v>
+        <v>201000</v>
       </c>
       <c r="E58" s="3">
-        <v>371300</v>
+        <v>378900</v>
       </c>
       <c r="F58" s="3">
-        <v>272900</v>
+        <v>278500</v>
       </c>
       <c r="G58" s="3">
-        <v>144200</v>
+        <v>147100</v>
       </c>
       <c r="H58" s="3">
-        <v>151100</v>
+        <v>154200</v>
       </c>
       <c r="I58" s="3">
-        <v>917300</v>
+        <v>936000</v>
       </c>
       <c r="J58" s="3">
-        <v>230400</v>
+        <v>235100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1649500</v>
+        <v>1683200</v>
       </c>
       <c r="E59" s="3">
-        <v>1495000</v>
+        <v>1525500</v>
       </c>
       <c r="F59" s="3">
-        <v>1471500</v>
+        <v>1501600</v>
       </c>
       <c r="G59" s="3">
-        <v>1427800</v>
+        <v>1456900</v>
       </c>
       <c r="H59" s="3">
-        <v>1248900</v>
+        <v>1274400</v>
       </c>
       <c r="I59" s="3">
-        <v>1060600</v>
+        <v>1082200</v>
       </c>
       <c r="J59" s="3">
-        <v>849000</v>
+        <v>866400</v>
       </c>
       <c r="K59" s="3">
         <v>863000</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4231000</v>
+        <v>4317400</v>
       </c>
       <c r="E60" s="3">
-        <v>3941200</v>
+        <v>4021600</v>
       </c>
       <c r="F60" s="3">
-        <v>3560500</v>
+        <v>3633200</v>
       </c>
       <c r="G60" s="3">
-        <v>3670800</v>
+        <v>3745700</v>
       </c>
       <c r="H60" s="3">
-        <v>3305600</v>
+        <v>3373000</v>
       </c>
       <c r="I60" s="3">
-        <v>3584700</v>
+        <v>3657900</v>
       </c>
       <c r="J60" s="3">
-        <v>2660600</v>
+        <v>2714900</v>
       </c>
       <c r="K60" s="3">
         <v>2013700</v>
@@ -2853,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>8900</v>
+        <v>9100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>565800</v>
+        <v>577300</v>
       </c>
       <c r="K61" s="3">
         <v>605000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>433600</v>
+        <v>442500</v>
       </c>
       <c r="E62" s="3">
-        <v>397400</v>
+        <v>405500</v>
       </c>
       <c r="F62" s="3">
-        <v>371400</v>
+        <v>379000</v>
       </c>
       <c r="G62" s="3">
-        <v>412600</v>
+        <v>421000</v>
       </c>
       <c r="H62" s="3">
-        <v>323700</v>
+        <v>330300</v>
       </c>
       <c r="I62" s="3">
-        <v>56100</v>
+        <v>57200</v>
       </c>
       <c r="J62" s="3">
-        <v>52500</v>
+        <v>53500</v>
       </c>
       <c r="K62" s="3">
         <v>48000</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4885500</v>
+        <v>4985200</v>
       </c>
       <c r="E66" s="3">
-        <v>4521100</v>
+        <v>4613400</v>
       </c>
       <c r="F66" s="3">
-        <v>4097100</v>
+        <v>4180700</v>
       </c>
       <c r="G66" s="3">
-        <v>4206000</v>
+        <v>4291900</v>
       </c>
       <c r="H66" s="3">
-        <v>3696500</v>
+        <v>3772000</v>
       </c>
       <c r="I66" s="3">
-        <v>3633700</v>
+        <v>3707900</v>
       </c>
       <c r="J66" s="3">
-        <v>3272800</v>
+        <v>3339600</v>
       </c>
       <c r="K66" s="3">
         <v>2673500</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>5089400</v>
+        <v>5193300</v>
       </c>
       <c r="E72" s="3">
-        <v>3968000</v>
+        <v>4049000</v>
       </c>
       <c r="F72" s="3">
-        <v>3097800</v>
+        <v>3161000</v>
       </c>
       <c r="G72" s="3">
-        <v>2451000</v>
+        <v>2501000</v>
       </c>
       <c r="H72" s="3">
-        <v>1647500</v>
+        <v>1681100</v>
       </c>
       <c r="I72" s="3">
-        <v>1092500</v>
+        <v>1114800</v>
       </c>
       <c r="J72" s="3">
-        <v>774100</v>
+        <v>789900</v>
       </c>
       <c r="K72" s="3">
         <v>504400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5106600</v>
+        <v>5210800</v>
       </c>
       <c r="E76" s="3">
-        <v>4525000</v>
+        <v>4617400</v>
       </c>
       <c r="F76" s="3">
-        <v>4508600</v>
+        <v>4600600</v>
       </c>
       <c r="G76" s="3">
-        <v>3937200</v>
+        <v>4017600</v>
       </c>
       <c r="H76" s="3">
-        <v>3015600</v>
+        <v>3077200</v>
       </c>
       <c r="I76" s="3">
-        <v>2384900</v>
+        <v>2433600</v>
       </c>
       <c r="J76" s="3">
-        <v>1974900</v>
+        <v>2015200</v>
       </c>
       <c r="K76" s="3">
         <v>791500</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1121400</v>
+        <v>1144300</v>
       </c>
       <c r="E81" s="3">
-        <v>870200</v>
+        <v>888000</v>
       </c>
       <c r="F81" s="3">
-        <v>646700</v>
+        <v>659900</v>
       </c>
       <c r="G81" s="3">
-        <v>816100</v>
+        <v>832800</v>
       </c>
       <c r="H81" s="3">
-        <v>555000</v>
+        <v>566300</v>
       </c>
       <c r="I81" s="3">
-        <v>294100</v>
+        <v>300100</v>
       </c>
       <c r="J81" s="3">
-        <v>269400</v>
+        <v>274900</v>
       </c>
       <c r="K81" s="3">
         <v>281200</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>210100</v>
+        <v>214400</v>
       </c>
       <c r="E83" s="3">
-        <v>195300</v>
+        <v>199300</v>
       </c>
       <c r="F83" s="3">
-        <v>174000</v>
+        <v>177600</v>
       </c>
       <c r="G83" s="3">
-        <v>157400</v>
+        <v>160600</v>
       </c>
       <c r="H83" s="3">
-        <v>131300</v>
+        <v>134000</v>
       </c>
       <c r="I83" s="3">
-        <v>122900</v>
+        <v>125400</v>
       </c>
       <c r="J83" s="3">
-        <v>154400</v>
+        <v>157500</v>
       </c>
       <c r="K83" s="3">
         <v>139800</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1991500</v>
+        <v>2032200</v>
       </c>
       <c r="E89" s="3">
-        <v>1453400</v>
+        <v>1483100</v>
       </c>
       <c r="F89" s="3">
-        <v>931800</v>
+        <v>950900</v>
       </c>
       <c r="G89" s="3">
-        <v>1633100</v>
+        <v>1666400</v>
       </c>
       <c r="H89" s="3">
-        <v>1698000</v>
+        <v>1732700</v>
       </c>
       <c r="I89" s="3">
-        <v>793800</v>
+        <v>810000</v>
       </c>
       <c r="J89" s="3">
-        <v>135600</v>
+        <v>138300</v>
       </c>
       <c r="K89" s="3">
         <v>391000</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-722700</v>
+        <v>-737400</v>
       </c>
       <c r="E91" s="3">
-        <v>-428700</v>
+        <v>-437400</v>
       </c>
       <c r="F91" s="3">
-        <v>-494400</v>
+        <v>-504500</v>
       </c>
       <c r="G91" s="3">
-        <v>-313900</v>
+        <v>-320300</v>
       </c>
       <c r="H91" s="3">
-        <v>-591000</v>
+        <v>-603100</v>
       </c>
       <c r="I91" s="3">
-        <v>-496500</v>
+        <v>-506700</v>
       </c>
       <c r="J91" s="3">
-        <v>-341900</v>
+        <v>-348800</v>
       </c>
       <c r="K91" s="3">
         <v>-300000</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-713000</v>
+        <v>-727500</v>
       </c>
       <c r="E94" s="3">
-        <v>145000</v>
+        <v>147900</v>
       </c>
       <c r="F94" s="3">
-        <v>-321400</v>
+        <v>-328000</v>
       </c>
       <c r="G94" s="3">
-        <v>-925000</v>
+        <v>-943900</v>
       </c>
       <c r="H94" s="3">
-        <v>-1138500</v>
+        <v>-1161800</v>
       </c>
       <c r="I94" s="3">
-        <v>-924800</v>
+        <v>-943700</v>
       </c>
       <c r="J94" s="3">
-        <v>-280800</v>
+        <v>-286600</v>
       </c>
       <c r="K94" s="3">
         <v>-230500</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-849100</v>
+        <v>-866500</v>
       </c>
       <c r="E100" s="3">
-        <v>-770000</v>
+        <v>-785700</v>
       </c>
       <c r="F100" s="3">
-        <v>-8100</v>
+        <v>-8300</v>
       </c>
       <c r="G100" s="3">
         <v>-2900</v>
       </c>
       <c r="H100" s="3">
-        <v>-864400</v>
+        <v>-882100</v>
       </c>
       <c r="I100" s="3">
-        <v>81100</v>
+        <v>82800</v>
       </c>
       <c r="J100" s="3">
-        <v>990600</v>
+        <v>1010800</v>
       </c>
       <c r="K100" s="3">
         <v>-54300</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>11900</v>
+        <v>12100</v>
       </c>
       <c r="E101" s="3">
-        <v>-8700</v>
+        <v>-8900</v>
       </c>
       <c r="F101" s="3">
         <v>100</v>
       </c>
       <c r="G101" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="H101" s="3">
-        <v>-15500</v>
+        <v>-15800</v>
       </c>
       <c r="I101" s="3">
-        <v>24500</v>
+        <v>25000</v>
       </c>
       <c r="J101" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="K101" s="3">
         <v>2200</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>441300</v>
+        <v>450300</v>
       </c>
       <c r="E102" s="3">
-        <v>819600</v>
+        <v>836300</v>
       </c>
       <c r="F102" s="3">
-        <v>602400</v>
+        <v>614700</v>
       </c>
       <c r="G102" s="3">
-        <v>703500</v>
+        <v>717900</v>
       </c>
       <c r="H102" s="3">
-        <v>-320400</v>
+        <v>-327000</v>
       </c>
       <c r="I102" s="3">
-        <v>-25400</v>
+        <v>-25900</v>
       </c>
       <c r="J102" s="3">
-        <v>844500</v>
+        <v>861700</v>
       </c>
       <c r="K102" s="3">
         <v>108400</v>

--- a/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>VIPS</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>15910400</v>
+        <v>15915600</v>
       </c>
       <c r="E8" s="3">
-        <v>14542400</v>
+        <v>14955700</v>
       </c>
       <c r="F8" s="3">
-        <v>16503100</v>
+        <v>18427100</v>
       </c>
       <c r="G8" s="3">
-        <v>14360000</v>
+        <v>15601900</v>
       </c>
       <c r="H8" s="3">
-        <v>13110400</v>
+        <v>13355700</v>
       </c>
       <c r="I8" s="3">
-        <v>11916200</v>
+        <v>12289600</v>
       </c>
       <c r="J8" s="3">
-        <v>10279200</v>
+        <v>11205700</v>
       </c>
       <c r="K8" s="3">
         <v>7814100</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>12284300</v>
+        <v>12288300</v>
       </c>
       <c r="E9" s="3">
-        <v>11495000</v>
+        <v>11821700</v>
       </c>
       <c r="F9" s="3">
-        <v>13245500</v>
+        <v>14789700</v>
       </c>
       <c r="G9" s="3">
-        <v>11359200</v>
+        <v>12341600</v>
       </c>
       <c r="H9" s="3">
-        <v>10194900</v>
+        <v>10385600</v>
       </c>
       <c r="I9" s="3">
-        <v>9509800</v>
+        <v>9807800</v>
       </c>
       <c r="J9" s="3">
-        <v>7982100</v>
+        <v>8701600</v>
       </c>
       <c r="K9" s="3">
         <v>5936700</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3626100</v>
+        <v>3627300</v>
       </c>
       <c r="E10" s="3">
-        <v>3047400</v>
+        <v>3134000</v>
       </c>
       <c r="F10" s="3">
-        <v>3257600</v>
+        <v>3637300</v>
       </c>
       <c r="G10" s="3">
-        <v>3000800</v>
+        <v>3260300</v>
       </c>
       <c r="H10" s="3">
-        <v>2915500</v>
+        <v>2970100</v>
       </c>
       <c r="I10" s="3">
-        <v>2406400</v>
+        <v>2481800</v>
       </c>
       <c r="J10" s="3">
-        <v>2297100</v>
+        <v>2504200</v>
       </c>
       <c r="K10" s="3">
         <v>1877400</v>
@@ -879,26 +879,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>249300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>232800</v>
+      </c>
+      <c r="F12" s="3">
+        <v>238800</v>
+      </c>
+      <c r="G12" s="3">
+        <v>187100</v>
+      </c>
+      <c r="H12" s="3">
+        <v>225200</v>
+      </c>
+      <c r="I12" s="3">
+        <v>290900</v>
+      </c>
+      <c r="J12" s="3">
+        <v>277900</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>24700</v>
+        <v>4200</v>
       </c>
       <c r="E14" s="3">
-        <v>47000</v>
+        <v>-21600</v>
       </c>
       <c r="F14" s="3">
-        <v>58500</v>
+        <v>34800</v>
       </c>
       <c r="G14" s="3">
-        <v>6100</v>
+        <v>-156900</v>
       </c>
       <c r="H14" s="3">
-        <v>57200</v>
+        <v>99700</v>
       </c>
       <c r="I14" s="3">
-        <v>2800</v>
+        <v>-39700</v>
       </c>
       <c r="J14" s="3">
-        <v>18800</v>
+        <v>700</v>
       </c>
       <c r="K14" s="3">
         <v>15800</v>
@@ -1014,26 +1014,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>179000</v>
+      </c>
+      <c r="F15" s="3">
+        <v>174600</v>
+      </c>
+      <c r="G15" s="3">
+        <v>154200</v>
       </c>
       <c r="H15" s="3">
-        <v>117100</v>
+        <v>121500</v>
       </c>
       <c r="I15" s="3">
-        <v>108600</v>
+        <v>119000</v>
       </c>
       <c r="J15" s="3">
-        <v>101600</v>
+        <v>163200</v>
       </c>
       <c r="K15" s="3">
         <v>84400</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14629600</v>
+        <v>14632700</v>
       </c>
       <c r="E17" s="3">
-        <v>13682000</v>
+        <v>14013200</v>
       </c>
       <c r="F17" s="3">
-        <v>15774500</v>
+        <v>17565300</v>
       </c>
       <c r="G17" s="3">
-        <v>13539900</v>
+        <v>14717600</v>
       </c>
       <c r="H17" s="3">
-        <v>12455400</v>
+        <v>12564800</v>
       </c>
       <c r="I17" s="3">
-        <v>11577700</v>
+        <v>11952200</v>
       </c>
       <c r="J17" s="3">
-        <v>9918600</v>
+        <v>10803500</v>
       </c>
       <c r="K17" s="3">
         <v>7456100</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1280800</v>
+        <v>1282900</v>
       </c>
       <c r="E18" s="3">
-        <v>860500</v>
+        <v>942500</v>
       </c>
       <c r="F18" s="3">
-        <v>728500</v>
+        <v>861800</v>
       </c>
       <c r="G18" s="3">
-        <v>820100</v>
+        <v>884300</v>
       </c>
       <c r="H18" s="3">
-        <v>655000</v>
+        <v>790900</v>
       </c>
       <c r="I18" s="3">
-        <v>338500</v>
+        <v>337300</v>
       </c>
       <c r="J18" s="3">
-        <v>360500</v>
+        <v>402200</v>
       </c>
       <c r="K18" s="3">
         <v>358100</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>130400</v>
+        <v>-34300</v>
       </c>
       <c r="E20" s="3">
-        <v>281700</v>
+        <v>-98800</v>
       </c>
       <c r="F20" s="3">
-        <v>101500</v>
+        <v>-800</v>
       </c>
       <c r="G20" s="3">
-        <v>179000</v>
+        <v>19900</v>
       </c>
       <c r="H20" s="3">
-        <v>54000</v>
+        <v>-3800</v>
       </c>
       <c r="I20" s="3">
-        <v>71300</v>
+        <v>-3500</v>
       </c>
       <c r="J20" s="3">
-        <v>9300</v>
+        <v>17400</v>
       </c>
       <c r="K20" s="3">
         <v>21800</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1624800</v>
+        <v>1500900</v>
       </c>
       <c r="E21" s="3">
-        <v>1340700</v>
+        <v>1220300</v>
       </c>
       <c r="F21" s="3">
-        <v>1007000</v>
+        <v>1037200</v>
       </c>
       <c r="G21" s="3">
-        <v>1159200</v>
+        <v>1018600</v>
       </c>
       <c r="H21" s="3">
-        <v>842500</v>
+        <v>916200</v>
       </c>
       <c r="I21" s="3">
-        <v>534800</v>
+        <v>459800</v>
       </c>
       <c r="J21" s="3">
-        <v>526800</v>
+        <v>548000</v>
       </c>
       <c r="K21" s="3">
         <v>519600</v>
@@ -1278,22 +1278,22 @@
         <v>3200</v>
       </c>
       <c r="E22" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="F22" s="3">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="G22" s="3">
-        <v>9500</v>
+        <v>10300</v>
       </c>
       <c r="H22" s="3">
-        <v>12100</v>
+        <v>12400</v>
       </c>
       <c r="I22" s="3">
-        <v>22500</v>
+        <v>23200</v>
       </c>
       <c r="J22" s="3">
-        <v>11600</v>
+        <v>12700</v>
       </c>
       <c r="K22" s="3">
         <v>11800</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1408000</v>
+        <v>1419700</v>
       </c>
       <c r="E23" s="3">
-        <v>1138700</v>
+        <v>1170100</v>
       </c>
       <c r="F23" s="3">
-        <v>828000</v>
+        <v>931200</v>
       </c>
       <c r="G23" s="3">
-        <v>989600</v>
+        <v>1079800</v>
       </c>
       <c r="H23" s="3">
-        <v>696800</v>
+        <v>713800</v>
       </c>
       <c r="I23" s="3">
-        <v>387300</v>
+        <v>392600</v>
       </c>
       <c r="J23" s="3">
-        <v>358200</v>
+        <v>387100</v>
       </c>
       <c r="K23" s="3">
         <v>368100</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>263100</v>
+        <v>263200</v>
       </c>
       <c r="E24" s="3">
-        <v>248000</v>
+        <v>255000</v>
       </c>
       <c r="F24" s="3">
-        <v>172400</v>
+        <v>192500</v>
       </c>
       <c r="G24" s="3">
-        <v>159300</v>
+        <v>173100</v>
       </c>
       <c r="H24" s="3">
-        <v>138700</v>
+        <v>141300</v>
       </c>
       <c r="I24" s="3">
-        <v>79900</v>
+        <v>82400</v>
       </c>
       <c r="J24" s="3">
-        <v>88300</v>
+        <v>96200</v>
       </c>
       <c r="K24" s="3">
         <v>83100</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1144900</v>
+        <v>1156600</v>
       </c>
       <c r="E26" s="3">
-        <v>890800</v>
+        <v>915100</v>
       </c>
       <c r="F26" s="3">
-        <v>655600</v>
+        <v>738700</v>
       </c>
       <c r="G26" s="3">
-        <v>830300</v>
+        <v>906700</v>
       </c>
       <c r="H26" s="3">
-        <v>558200</v>
+        <v>572500</v>
       </c>
       <c r="I26" s="3">
-        <v>307400</v>
+        <v>310200</v>
       </c>
       <c r="J26" s="3">
-        <v>269900</v>
+        <v>290800</v>
       </c>
       <c r="K26" s="3">
         <v>285000</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1144300</v>
+        <v>1144700</v>
       </c>
       <c r="E27" s="3">
-        <v>888000</v>
+        <v>913200</v>
       </c>
       <c r="F27" s="3">
-        <v>659900</v>
+        <v>736900</v>
       </c>
       <c r="G27" s="3">
-        <v>832800</v>
+        <v>904800</v>
       </c>
       <c r="H27" s="3">
-        <v>566300</v>
+        <v>576900</v>
       </c>
       <c r="I27" s="3">
-        <v>300100</v>
+        <v>309500</v>
       </c>
       <c r="J27" s="3">
-        <v>274900</v>
+        <v>299600</v>
       </c>
       <c r="K27" s="3">
         <v>281200</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-130400</v>
+        <v>34300</v>
       </c>
       <c r="E32" s="3">
-        <v>-281700</v>
+        <v>98800</v>
       </c>
       <c r="F32" s="3">
-        <v>-101500</v>
+        <v>800</v>
       </c>
       <c r="G32" s="3">
-        <v>-179000</v>
+        <v>-19900</v>
       </c>
       <c r="H32" s="3">
-        <v>-54000</v>
+        <v>3800</v>
       </c>
       <c r="I32" s="3">
-        <v>-71300</v>
+        <v>3500</v>
       </c>
       <c r="J32" s="3">
-        <v>-9300</v>
+        <v>-17400</v>
       </c>
       <c r="K32" s="3">
         <v>-21800</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1144300</v>
+        <v>1144700</v>
       </c>
       <c r="E33" s="3">
-        <v>888000</v>
+        <v>913200</v>
       </c>
       <c r="F33" s="3">
-        <v>659900</v>
+        <v>736900</v>
       </c>
       <c r="G33" s="3">
-        <v>832800</v>
+        <v>904800</v>
       </c>
       <c r="H33" s="3">
-        <v>566300</v>
+        <v>576900</v>
       </c>
       <c r="I33" s="3">
-        <v>300100</v>
+        <v>309500</v>
       </c>
       <c r="J33" s="3">
-        <v>274900</v>
+        <v>299600</v>
       </c>
       <c r="K33" s="3">
         <v>281200</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1144300</v>
+        <v>1144700</v>
       </c>
       <c r="E35" s="3">
-        <v>888000</v>
+        <v>913200</v>
       </c>
       <c r="F35" s="3">
-        <v>659900</v>
+        <v>736900</v>
       </c>
       <c r="G35" s="3">
-        <v>832800</v>
+        <v>904800</v>
       </c>
       <c r="H35" s="3">
-        <v>566300</v>
+        <v>576900</v>
       </c>
       <c r="I35" s="3">
-        <v>300100</v>
+        <v>309500</v>
       </c>
       <c r="J35" s="3">
-        <v>274900</v>
+        <v>299600</v>
       </c>
       <c r="K35" s="3">
         <v>281200</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3583000</v>
+        <v>3584100</v>
       </c>
       <c r="E41" s="3">
-        <v>3092900</v>
+        <v>3180800</v>
       </c>
       <c r="F41" s="3">
-        <v>2297600</v>
+        <v>2565500</v>
       </c>
       <c r="G41" s="3">
-        <v>1691100</v>
+        <v>1837400</v>
       </c>
       <c r="H41" s="3">
-        <v>926800</v>
+        <v>944100</v>
       </c>
       <c r="I41" s="3">
-        <v>1345000</v>
+        <v>1387200</v>
       </c>
       <c r="J41" s="3">
-        <v>1406100</v>
+        <v>1532900</v>
       </c>
       <c r="K41" s="3">
         <v>567500</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>279600</v>
+        <v>350300</v>
       </c>
       <c r="E42" s="3">
-        <v>225000</v>
+        <v>322800</v>
       </c>
       <c r="F42" s="3">
-        <v>758700</v>
+        <v>959300</v>
       </c>
       <c r="G42" s="3">
-        <v>1033200</v>
+        <v>1151600</v>
       </c>
       <c r="H42" s="3">
-        <v>430400</v>
+        <v>485000</v>
       </c>
       <c r="I42" s="3">
-        <v>327200</v>
+        <v>337500</v>
       </c>
       <c r="J42" s="3">
-        <v>34700</v>
+        <v>37800</v>
       </c>
       <c r="K42" s="3">
         <v>92800</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>512500</v>
+        <v>341400</v>
       </c>
       <c r="E43" s="3">
-        <v>496100</v>
+        <v>308800</v>
       </c>
       <c r="F43" s="3">
-        <v>482700</v>
+        <v>315900</v>
       </c>
       <c r="G43" s="3">
-        <v>420400</v>
+        <v>304000</v>
       </c>
       <c r="H43" s="3">
-        <v>641100</v>
+        <v>486000</v>
       </c>
       <c r="I43" s="3">
-        <v>1353100</v>
+        <v>1178400</v>
       </c>
       <c r="J43" s="3">
-        <v>1196600</v>
+        <v>863500</v>
       </c>
       <c r="K43" s="3">
         <v>627400</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>795800</v>
+        <v>853100</v>
       </c>
       <c r="E44" s="3">
-        <v>777600</v>
+        <v>865000</v>
       </c>
       <c r="F44" s="3">
-        <v>967800</v>
+        <v>1141400</v>
       </c>
       <c r="G44" s="3">
-        <v>1077400</v>
+        <v>1263800</v>
       </c>
       <c r="H44" s="3">
-        <v>1086700</v>
+        <v>1107100</v>
       </c>
       <c r="I44" s="3">
-        <v>756800</v>
+        <v>780500</v>
       </c>
       <c r="J44" s="3">
-        <v>981300</v>
+        <v>1069700</v>
       </c>
       <c r="K44" s="3">
         <v>683300</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>124400</v>
+        <v>32800</v>
       </c>
       <c r="E45" s="3">
-        <v>164200</v>
+        <v>36100</v>
       </c>
       <c r="F45" s="3">
-        <v>123200</v>
+        <v>40200</v>
       </c>
       <c r="G45" s="3">
-        <v>172700</v>
+        <v>84600</v>
       </c>
       <c r="H45" s="3">
-        <v>161500</v>
+        <v>111700</v>
       </c>
       <c r="I45" s="3">
-        <v>70200</v>
+        <v>199700</v>
       </c>
       <c r="J45" s="3">
-        <v>35000</v>
+        <v>417600</v>
       </c>
       <c r="K45" s="3">
         <v>42400</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5295300</v>
+        <v>5297000</v>
       </c>
       <c r="E46" s="3">
-        <v>4755900</v>
+        <v>4891000</v>
       </c>
       <c r="F46" s="3">
-        <v>4630100</v>
+        <v>5169800</v>
       </c>
       <c r="G46" s="3">
-        <v>4394800</v>
+        <v>4774800</v>
       </c>
       <c r="H46" s="3">
-        <v>3246500</v>
+        <v>3307200</v>
       </c>
       <c r="I46" s="3">
-        <v>3852400</v>
+        <v>3973100</v>
       </c>
       <c r="J46" s="3">
-        <v>3653700</v>
+        <v>3983000</v>
       </c>
       <c r="K46" s="3">
         <v>2013300</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>715000</v>
+        <v>715200</v>
       </c>
       <c r="E47" s="3">
-        <v>680000</v>
+        <v>699300</v>
       </c>
       <c r="F47" s="3">
-        <v>699200</v>
+        <v>780700</v>
       </c>
       <c r="G47" s="3">
-        <v>678200</v>
+        <v>736900</v>
       </c>
       <c r="H47" s="3">
-        <v>735600</v>
+        <v>734700</v>
       </c>
       <c r="I47" s="3">
-        <v>301400</v>
+        <v>310900</v>
       </c>
       <c r="J47" s="3">
-        <v>84600</v>
+        <v>92300</v>
       </c>
       <c r="K47" s="3">
         <v>138700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2458100</v>
+        <v>2458900</v>
       </c>
       <c r="E48" s="3">
-        <v>2413200</v>
+        <v>2481800</v>
       </c>
       <c r="F48" s="3">
-        <v>2188700</v>
+        <v>2443900</v>
       </c>
       <c r="G48" s="3">
-        <v>2138000</v>
+        <v>2322900</v>
       </c>
       <c r="H48" s="3">
-        <v>1828800</v>
+        <v>1863100</v>
       </c>
       <c r="I48" s="3">
-        <v>1202800</v>
+        <v>1240500</v>
       </c>
       <c r="J48" s="3">
-        <v>939000</v>
+        <v>1023700</v>
       </c>
       <c r="K48" s="3">
         <v>616900</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>153400</v>
+        <v>1582400</v>
       </c>
       <c r="E49" s="3">
-        <v>153900</v>
+        <v>1265800</v>
       </c>
       <c r="F49" s="3">
-        <v>128300</v>
+        <v>1184100</v>
       </c>
       <c r="G49" s="3">
-        <v>130600</v>
+        <v>1070600</v>
       </c>
       <c r="H49" s="3">
-        <v>80900</v>
+        <v>878200</v>
       </c>
       <c r="I49" s="3">
-        <v>101500</v>
+        <v>669700</v>
       </c>
       <c r="J49" s="3">
-        <v>108300</v>
+        <v>591100</v>
       </c>
       <c r="K49" s="3">
         <v>150800</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1574200</v>
+        <v>49100</v>
       </c>
       <c r="E52" s="3">
-        <v>1227800</v>
+        <v>56300</v>
       </c>
       <c r="F52" s="3">
-        <v>1135000</v>
+        <v>100000</v>
       </c>
       <c r="G52" s="3">
-        <v>967800</v>
+        <v>11300</v>
       </c>
       <c r="H52" s="3">
-        <v>957300</v>
+        <v>15200</v>
       </c>
       <c r="I52" s="3">
-        <v>683400</v>
+        <v>41100</v>
       </c>
       <c r="J52" s="3">
-        <v>569200</v>
+        <v>84200</v>
       </c>
       <c r="K52" s="3">
         <v>545400</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>10196000</v>
+        <v>10199400</v>
       </c>
       <c r="E54" s="3">
-        <v>9230700</v>
+        <v>9493100</v>
       </c>
       <c r="F54" s="3">
-        <v>8781300</v>
+        <v>9805000</v>
       </c>
       <c r="G54" s="3">
-        <v>8309500</v>
+        <v>9028100</v>
       </c>
       <c r="H54" s="3">
-        <v>6849200</v>
+        <v>6977400</v>
       </c>
       <c r="I54" s="3">
-        <v>6141500</v>
+        <v>6333900</v>
       </c>
       <c r="J54" s="3">
-        <v>5354800</v>
+        <v>5837500</v>
       </c>
       <c r="K54" s="3">
         <v>3465000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2433200</v>
+        <v>2449100</v>
       </c>
       <c r="E57" s="3">
-        <v>2117300</v>
+        <v>2198700</v>
       </c>
       <c r="F57" s="3">
-        <v>1853200</v>
+        <v>2125500</v>
       </c>
       <c r="G57" s="3">
-        <v>2141700</v>
+        <v>2385500</v>
       </c>
       <c r="H57" s="3">
-        <v>1944400</v>
+        <v>2057300</v>
       </c>
       <c r="I57" s="3">
-        <v>1639600</v>
+        <v>1738000</v>
       </c>
       <c r="J57" s="3">
-        <v>1613500</v>
+        <v>1769000</v>
       </c>
       <c r="K57" s="3">
         <v>1150700</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>201000</v>
+        <v>239000</v>
       </c>
       <c r="E58" s="3">
-        <v>378900</v>
+        <v>429400</v>
       </c>
       <c r="F58" s="3">
-        <v>278500</v>
+        <v>378000</v>
       </c>
       <c r="G58" s="3">
-        <v>147100</v>
+        <v>215100</v>
       </c>
       <c r="H58" s="3">
-        <v>154200</v>
+        <v>204900</v>
       </c>
       <c r="I58" s="3">
-        <v>936000</v>
+        <v>965400</v>
       </c>
       <c r="J58" s="3">
-        <v>235100</v>
+        <v>256200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1683200</v>
+        <v>988400</v>
       </c>
       <c r="E59" s="3">
-        <v>1525500</v>
+        <v>887800</v>
       </c>
       <c r="F59" s="3">
-        <v>1501600</v>
+        <v>825600</v>
       </c>
       <c r="G59" s="3">
-        <v>1456900</v>
+        <v>719500</v>
       </c>
       <c r="H59" s="3">
-        <v>1274400</v>
+        <v>602000</v>
       </c>
       <c r="I59" s="3">
-        <v>1082200</v>
+        <v>526900</v>
       </c>
       <c r="J59" s="3">
-        <v>866400</v>
+        <v>615700</v>
       </c>
       <c r="K59" s="3">
         <v>863000</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4317400</v>
+        <v>4318800</v>
       </c>
       <c r="E60" s="3">
-        <v>4021600</v>
+        <v>4135900</v>
       </c>
       <c r="F60" s="3">
-        <v>3633200</v>
+        <v>4056800</v>
       </c>
       <c r="G60" s="3">
-        <v>3745700</v>
+        <v>4069600</v>
       </c>
       <c r="H60" s="3">
-        <v>3373000</v>
+        <v>3436200</v>
       </c>
       <c r="I60" s="3">
-        <v>3657900</v>
+        <v>3772500</v>
       </c>
       <c r="J60" s="3">
-        <v>2714900</v>
+        <v>2959700</v>
       </c>
       <c r="K60" s="3">
         <v>2013700</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>97200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>120800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>208500</v>
       </c>
       <c r="H61" s="3">
-        <v>9100</v>
+        <v>209700</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>577300</v>
+        <v>629300</v>
       </c>
       <c r="K61" s="3">
         <v>605000</v>
@@ -2885,26 +2885,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>442500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>405500</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F62" s="3">
-        <v>379000</v>
+        <v>42800</v>
       </c>
       <c r="G62" s="3">
-        <v>421000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>330300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>57200</v>
-      </c>
-      <c r="J62" s="3">
-        <v>53500</v>
+        <v>18600</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>48000</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4985200</v>
+        <v>4761400</v>
       </c>
       <c r="E66" s="3">
-        <v>4613400</v>
+        <v>4552900</v>
       </c>
       <c r="F66" s="3">
-        <v>4180700</v>
+        <v>4479900</v>
       </c>
       <c r="G66" s="3">
-        <v>4291900</v>
+        <v>4527000</v>
       </c>
       <c r="H66" s="3">
-        <v>3772000</v>
+        <v>3781900</v>
       </c>
       <c r="I66" s="3">
-        <v>3707900</v>
+        <v>3831500</v>
       </c>
       <c r="J66" s="3">
-        <v>3339600</v>
+        <v>3647400</v>
       </c>
       <c r="K66" s="3">
         <v>2673500</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>5193300</v>
+        <v>5195000</v>
       </c>
       <c r="E72" s="3">
-        <v>4049000</v>
+        <v>4164100</v>
       </c>
       <c r="F72" s="3">
-        <v>3161000</v>
+        <v>3529500</v>
       </c>
       <c r="G72" s="3">
-        <v>2501000</v>
+        <v>2717300</v>
       </c>
       <c r="H72" s="3">
-        <v>1681100</v>
+        <v>1712500</v>
       </c>
       <c r="I72" s="3">
-        <v>1114800</v>
+        <v>1149700</v>
       </c>
       <c r="J72" s="3">
-        <v>789900</v>
+        <v>861100</v>
       </c>
       <c r="K72" s="3">
         <v>504400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5210800</v>
+        <v>5212500</v>
       </c>
       <c r="E76" s="3">
-        <v>4617400</v>
+        <v>4748600</v>
       </c>
       <c r="F76" s="3">
-        <v>4600600</v>
+        <v>5136900</v>
       </c>
       <c r="G76" s="3">
-        <v>4017600</v>
+        <v>4365100</v>
       </c>
       <c r="H76" s="3">
-        <v>3077200</v>
+        <v>3134800</v>
       </c>
       <c r="I76" s="3">
-        <v>2433600</v>
+        <v>2509800</v>
       </c>
       <c r="J76" s="3">
-        <v>2015200</v>
+        <v>2196900</v>
       </c>
       <c r="K76" s="3">
         <v>791500</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1144300</v>
+        <v>1144700</v>
       </c>
       <c r="E81" s="3">
-        <v>888000</v>
+        <v>913200</v>
       </c>
       <c r="F81" s="3">
-        <v>659900</v>
+        <v>736900</v>
       </c>
       <c r="G81" s="3">
-        <v>832800</v>
+        <v>904800</v>
       </c>
       <c r="H81" s="3">
-        <v>566300</v>
+        <v>576900</v>
       </c>
       <c r="I81" s="3">
-        <v>300100</v>
+        <v>309500</v>
       </c>
       <c r="J81" s="3">
-        <v>274900</v>
+        <v>299600</v>
       </c>
       <c r="K81" s="3">
         <v>281200</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>214400</v>
+        <v>183200</v>
       </c>
       <c r="E83" s="3">
-        <v>199300</v>
+        <v>178500</v>
       </c>
       <c r="F83" s="3">
-        <v>177600</v>
+        <v>172700</v>
       </c>
       <c r="G83" s="3">
-        <v>160600</v>
+        <v>148600</v>
       </c>
       <c r="H83" s="3">
-        <v>134000</v>
+        <v>119300</v>
       </c>
       <c r="I83" s="3">
-        <v>125400</v>
+        <v>112000</v>
       </c>
       <c r="J83" s="3">
-        <v>157500</v>
+        <v>110800</v>
       </c>
       <c r="K83" s="3">
         <v>139800</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2032200</v>
+        <v>2032800</v>
       </c>
       <c r="E89" s="3">
-        <v>1483100</v>
+        <v>1525200</v>
       </c>
       <c r="F89" s="3">
-        <v>950900</v>
+        <v>1061700</v>
       </c>
       <c r="G89" s="3">
-        <v>1666400</v>
+        <v>1810600</v>
       </c>
       <c r="H89" s="3">
-        <v>1732700</v>
+        <v>1765100</v>
       </c>
       <c r="I89" s="3">
-        <v>810000</v>
+        <v>835400</v>
       </c>
       <c r="J89" s="3">
-        <v>138300</v>
+        <v>150800</v>
       </c>
       <c r="K89" s="3">
         <v>391000</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-737400</v>
+        <v>-305600</v>
       </c>
       <c r="E91" s="3">
-        <v>-437400</v>
+        <v>-352400</v>
       </c>
       <c r="F91" s="3">
-        <v>-504500</v>
+        <v>-430100</v>
       </c>
       <c r="G91" s="3">
-        <v>-320300</v>
+        <v>-342700</v>
       </c>
       <c r="H91" s="3">
-        <v>-603100</v>
+        <v>-474400</v>
       </c>
       <c r="I91" s="3">
-        <v>-506700</v>
+        <v>-366400</v>
       </c>
       <c r="J91" s="3">
-        <v>-348800</v>
+        <v>-337800</v>
       </c>
       <c r="K91" s="3">
         <v>-300000</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-727500</v>
+        <v>-727700</v>
       </c>
       <c r="E94" s="3">
-        <v>147900</v>
+        <v>152100</v>
       </c>
       <c r="F94" s="3">
-        <v>-328000</v>
+        <v>-366200</v>
       </c>
       <c r="G94" s="3">
-        <v>-943900</v>
+        <v>-1025500</v>
       </c>
       <c r="H94" s="3">
-        <v>-1161800</v>
+        <v>-1183500</v>
       </c>
       <c r="I94" s="3">
-        <v>-943700</v>
+        <v>-973300</v>
       </c>
       <c r="J94" s="3">
-        <v>-286600</v>
+        <v>-312400</v>
       </c>
       <c r="K94" s="3">
         <v>-230500</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-866500</v>
+        <v>-866700</v>
       </c>
       <c r="E100" s="3">
-        <v>-785700</v>
+        <v>-808100</v>
       </c>
       <c r="F100" s="3">
-        <v>-8300</v>
+        <v>-9300</v>
       </c>
       <c r="G100" s="3">
-        <v>-2900</v>
+        <v>-3200</v>
       </c>
       <c r="H100" s="3">
-        <v>-882100</v>
+        <v>-898600</v>
       </c>
       <c r="I100" s="3">
-        <v>82800</v>
+        <v>85300</v>
       </c>
       <c r="J100" s="3">
-        <v>1010800</v>
+        <v>1101900</v>
       </c>
       <c r="K100" s="3">
         <v>-54300</v>
@@ -4455,19 +4455,19 @@
         <v>12100</v>
       </c>
       <c r="E101" s="3">
-        <v>-8900</v>
+        <v>-9200</v>
       </c>
       <c r="F101" s="3">
         <v>100</v>
       </c>
       <c r="G101" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="H101" s="3">
-        <v>-15800</v>
+        <v>-16100</v>
       </c>
       <c r="I101" s="3">
-        <v>25000</v>
+        <v>25800</v>
       </c>
       <c r="J101" s="3">
         <v>-900</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>450300</v>
+        <v>450400</v>
       </c>
       <c r="E102" s="3">
-        <v>836300</v>
+        <v>860100</v>
       </c>
       <c r="F102" s="3">
-        <v>614700</v>
+        <v>686300</v>
       </c>
       <c r="G102" s="3">
-        <v>717900</v>
+        <v>780000</v>
       </c>
       <c r="H102" s="3">
-        <v>-327000</v>
+        <v>-333100</v>
       </c>
       <c r="I102" s="3">
-        <v>-25900</v>
+        <v>-26700</v>
       </c>
       <c r="J102" s="3">
-        <v>861700</v>
+        <v>939400</v>
       </c>
       <c r="K102" s="3">
         <v>108400</v>

--- a/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>VIPS</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14854000</v>
+      </c>
+      <c r="E8" s="3">
         <v>15915600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14955700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>18427100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15601900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13355700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12289600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11205700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7814100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5596300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3621100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1585200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>99300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11364600</v>
+      </c>
+      <c r="E9" s="3">
         <v>12288300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11821700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14789700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12341600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10385600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9807800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8701600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5936700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4218700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2720700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1204200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>77100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26700</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3489400</v>
+      </c>
+      <c r="E10" s="3">
         <v>3627300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3134000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3637300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3260300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2970100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2481800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2504200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1877400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1377600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>900400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>381000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>22200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6300</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,34 +886,35 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>259300</v>
+      </c>
+      <c r="E12" s="3">
         <v>249300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>232800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>238800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>187100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>225200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>290900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>277900</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -912,15 +925,18 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3">
         <v>1900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E14" s="3">
         <v>4200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-21600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>34800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-156900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>99700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-39700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>15800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>178500</v>
+      </c>
+      <c r="E15" s="3">
         <v>183800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>179000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>174600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>154200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>121500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>119000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>163200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>84400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>40600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>17200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>200</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13597200</v>
+      </c>
+      <c r="E17" s="3">
         <v>14632700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14013200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17565300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14717600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12564800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11952200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10803500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7456100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5322000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3491600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1534900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>101400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>48700</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1256800</v>
+      </c>
+      <c r="E18" s="3">
         <v>1282900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>942500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>861800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>884300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>790900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>337300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>402200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>358100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>274300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>129600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>50300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-34300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-98800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>19900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>17400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>21800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>23000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>48200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>15900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1454800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1500900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1220300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1037200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1018600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>916200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>459800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>548000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>519600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>378000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>234200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>67600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E22" s="3">
         <v>3200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>23200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11800</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1391200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1419700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1170100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>931200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1079800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>713800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>392600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>387100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>368100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>285400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>166000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>66200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>317200</v>
+      </c>
+      <c r="E24" s="3">
         <v>263200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>255000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>192500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>173100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>141300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>82400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>96200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>83100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>63700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>38400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>17300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1156600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>915100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>738700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>906700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>572500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>310200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>290800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>285000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>221700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>127600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>48900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1060400</v>
+      </c>
+      <c r="E27" s="3">
         <v>1144700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>913200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>736900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>904800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>576900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>309500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>299600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>281200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>221300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>131700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>48900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-22800</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E32" s="3">
         <v>34300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>98800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-19900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-17400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-21800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-23000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-48200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-15900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1060400</v>
+      </c>
+      <c r="E33" s="3">
         <v>1144700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>913200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>736900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>904800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>576900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>309500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>299600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>281200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>221300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>131700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>48900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-22800</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1060400</v>
+      </c>
+      <c r="E35" s="3">
         <v>1144700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>913200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>736900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>904800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>576900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>309500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>299600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>281200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>221300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>131700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>48900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-22800</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,313 +2072,332 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3610300</v>
+      </c>
+      <c r="E41" s="3">
         <v>3584100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3180800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2565500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1837400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>944100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1387200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1532900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>567500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>462800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>750000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>50900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6500</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>256600</v>
+      </c>
+      <c r="E42" s="3">
         <v>350300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>322800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>959300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1151600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>485000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>337500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>37800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>92800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>251600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>590000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>58700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>12400</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>540200</v>
+      </c>
+      <c r="E43" s="3">
         <v>341400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>308800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>315900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>304000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>486000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1178400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>863500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>627400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>306300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>155700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>689400</v>
+      </c>
+      <c r="E44" s="3">
         <v>853100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>865000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1141400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1263800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1107100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>780500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1069700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>683300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>635700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>561800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>41100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>20700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10100</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>32800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>36100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>40200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>84600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>111700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>199700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>417600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>42400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>35400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>52700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4400</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5179100</v>
+      </c>
+      <c r="E46" s="3">
         <v>5297000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4891000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5169800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4774800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3307200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3973100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3983000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2013300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1691700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2069800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>157700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>54800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>23000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>734000</v>
+      </c>
+      <c r="E47" s="3">
         <v>715200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>699300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>780700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>736900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>734700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>310900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>92300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>138700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>140900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>61100</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
@@ -2301,99 +2405,108 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2565600</v>
+      </c>
+      <c r="E48" s="3">
         <v>2458900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2481800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2443900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2322900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1863100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1240500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1023700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>616900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>410600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>598500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1300</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1612500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1582400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1265800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1184100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1070600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>878200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>669700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>591100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>150800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>118800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>172100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>800</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>82100</v>
+      </c>
+      <c r="E52" s="3">
         <v>49100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>56300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>100000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>41100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>84200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>545400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>427000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>64500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>600</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10266500</v>
+      </c>
+      <c r="E54" s="3">
         <v>10199400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9493100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9805000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9028100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6977400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6333900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5837500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3465000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2788900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2653900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>163100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>57200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>24400</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,233 +2784,249 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2081200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2449100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2198700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2125500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2385500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2057300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1738000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1769000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1150700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>925000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>958300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>72500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12800</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>336600</v>
+      </c>
+      <c r="E58" s="3">
         <v>239000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>429400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>378000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>215100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>204900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>965400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>256200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>13200</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1800</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>358400</v>
+      </c>
+      <c r="E59" s="3">
         <v>988400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>887800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>825600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>719500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>602000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>526900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>615700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>863000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>755300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>998000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>53500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7400</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4100100</v>
+      </c>
+      <c r="E60" s="3">
         <v>4318800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4135900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4056800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4069600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3436200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3772500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2959700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2013700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1693500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1589900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>126100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>45400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21700</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>81100</v>
+      </c>
+      <c r="E61" s="3">
         <v>97200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>120800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>150000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>208500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>209700</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>629300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>605000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>564900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>603500</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2891,14 +3036,14 @@
       <c r="E62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3">
         <v>42800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18600</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>8</v>
@@ -2906,17 +3051,17 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>48000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>27600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>38000</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>8</v>
@@ -2924,9 +3069,12 @@
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4574100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4761400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4552900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4479900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4527000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3781900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3831500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3647400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2673500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2296300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2254000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>126100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21700</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3256,11 +3423,14 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>8900</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5878300</v>
+      </c>
+      <c r="E72" s="3">
         <v>5195000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4164100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3529500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2717300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1712500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1149700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>861100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>504400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>225000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-18800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-25300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5475900</v>
+      </c>
+      <c r="E76" s="3">
         <v>5212500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4748600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5136900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4365100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3134800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2509800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2196900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>791500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>492700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>399900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>37000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1060400</v>
+      </c>
+      <c r="E81" s="3">
         <v>1144700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>913200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>736900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>904800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>576900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>309500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>299600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>281200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>221300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>131700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>48900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-22800</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>183200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>178500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>172700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>148600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>119300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>112000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>110800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>139800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>81300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>56500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>2032800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1525200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1061700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1810600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1765100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>835400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>150800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>391000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>266600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>510800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>66500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>16000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>200</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-305600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-352400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-430100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-342700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-474400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-366400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-337800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-321700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-266200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>-727700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>152100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-366200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1025500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1183500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-973300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-312400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-230500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-408900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-665900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-48800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,8 +4453,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4265,9 +4498,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-866700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-808100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-898600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>85300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1101900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-54300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-75000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>603100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>14100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>9700</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>12100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-16100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>25800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>13200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-15200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>450400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>860100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>686300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>780000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-333100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-26700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>939400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>108400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-204100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>432800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>32000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>11400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6400</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>VIPS</t>
   </si>
@@ -989,13 +989,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-11900</v>
+        <v>-36800</v>
       </c>
       <c r="E14" s="3">
         <v>4200</v>
       </c>
       <c r="F14" s="3">
-        <v>-21600</v>
+        <v>-55200</v>
       </c>
       <c r="G14" s="3">
         <v>34800</v>
@@ -1037,7 +1037,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>178500</v>
+        <v>194900</v>
       </c>
       <c r="E15" s="3">
         <v>183800</v>
@@ -1102,13 +1102,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13597200</v>
+        <v>13622100</v>
       </c>
       <c r="E17" s="3">
         <v>14632700</v>
       </c>
       <c r="F17" s="3">
-        <v>14013200</v>
+        <v>14046800</v>
       </c>
       <c r="G17" s="3">
         <v>17565300</v>
@@ -1150,13 +1150,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1256800</v>
+        <v>1231900</v>
       </c>
       <c r="E18" s="3">
         <v>1282900</v>
       </c>
       <c r="F18" s="3">
-        <v>942500</v>
+        <v>908900</v>
       </c>
       <c r="G18" s="3">
         <v>861800</v>
@@ -1266,13 +1266,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1454800</v>
+        <v>1446200</v>
       </c>
       <c r="E21" s="3">
         <v>1500900</v>
       </c>
       <c r="F21" s="3">
-        <v>1220300</v>
+        <v>1186700</v>
       </c>
       <c r="G21" s="3">
         <v>1037200</v>
@@ -2127,7 +2127,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>256600</v>
+        <v>263700</v>
       </c>
       <c r="E42" s="3">
         <v>350300</v>
@@ -2175,7 +2175,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>540200</v>
+        <v>455200</v>
       </c>
       <c r="E43" s="3">
         <v>341400</v>
@@ -2223,7 +2223,7 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>689400</v>
+        <v>731800</v>
       </c>
       <c r="E44" s="3">
         <v>853100</v>
@@ -2270,8 +2270,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>22300</v>
       </c>
       <c r="E45" s="3">
         <v>32800</v>
@@ -2791,7 +2791,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2081200</v>
+        <v>2095400</v>
       </c>
       <c r="E57" s="3">
         <v>2449100</v>
@@ -2839,7 +2839,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>336600</v>
+        <v>364800</v>
       </c>
       <c r="E58" s="3">
         <v>239000</v>
@@ -2887,7 +2887,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>358400</v>
+        <v>1081400</v>
       </c>
       <c r="E59" s="3">
         <v>988400</v>
@@ -3891,8 +3891,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>194300</v>
       </c>
       <c r="E83" s="3">
         <v>183200</v>
@@ -4179,8 +4179,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>1250700</v>
       </c>
       <c r="E89" s="3">
         <v>2032800</v>
@@ -4247,8 +4247,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
+      <c r="D91" s="3">
+        <v>-373100</v>
       </c>
       <c r="E91" s="3">
         <v>-305600</v>
@@ -4391,8 +4391,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>-488500</v>
       </c>
       <c r="E94" s="3">
         <v>-727700</v>
@@ -4460,7 +4460,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>230800</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4651,8 +4651,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>-680800</v>
       </c>
       <c r="E100" s="3">
         <v>-866700</v>
@@ -4699,8 +4699,8 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>8700</v>
       </c>
       <c r="E101" s="3">
         <v>12100</v>
@@ -4748,7 +4748,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="E102" s="3">
         <v>450400</v>

--- a/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VIPS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>VIPS</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15143500</v>
+      </c>
+      <c r="E8" s="3">
         <v>14854000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15915600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14955700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>18427100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15601900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13355700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12289600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11205700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7814100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5596300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3621100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1585200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>99300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11642100</v>
+      </c>
+      <c r="E9" s="3">
         <v>11364600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12288300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11821700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14789700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12341600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10385600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9807800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8701600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5936700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4218700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2720700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1204200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>77100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26700</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3501400</v>
+      </c>
+      <c r="E10" s="3">
         <v>3489400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3627300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3134000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3637300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3260300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2970100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2481800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2504200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1877400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1377600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>900400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>381000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>22200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6300</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,37 +899,38 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>250900</v>
+      </c>
+      <c r="E12" s="3">
         <v>259300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>249300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>232800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>238800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>187100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>225200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>290900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>277900</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -928,15 +941,18 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3">
         <v>1900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,105 +998,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-39800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-36800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-55200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>34800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-156900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>99700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-39700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>15800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>218800</v>
+      </c>
+      <c r="E15" s="3">
         <v>194900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>183800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>179000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>174600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>154200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>121500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>119000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>163200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>84400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>40600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>17200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>200</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14001600</v>
+      </c>
+      <c r="E17" s="3">
         <v>13622100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14632700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14046800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17565300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14717600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12564800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11952200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10803500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7456100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5322000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3491600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1534900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>101400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>48700</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1141900</v>
+      </c>
+      <c r="E18" s="3">
         <v>1231900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1282900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>908900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>861800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>884300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>790900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>337300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>402200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>358100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>274300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>129600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>50300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-15600</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-19500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-34300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-98800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>19900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>17400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>21800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>23000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>48200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>15900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1393800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1446200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1500900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1186700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1037200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1018600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>916200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>459800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>548000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>519600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>378000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>234200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>67600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-15300</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E22" s="3">
         <v>7900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>23200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11800</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1316600</v>
+      </c>
+      <c r="E23" s="3">
         <v>1391200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1419700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1170100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>931200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1079800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>713800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>392600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>387100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>368100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>285400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>166000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>66200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15600</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>257200</v>
+      </c>
+      <c r="E24" s="3">
         <v>317200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>263200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>255000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>192500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>173100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>141300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>82400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>96200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>83100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>63700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>38400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>17300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1059400</v>
+      </c>
+      <c r="E26" s="3">
         <v>1074000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1156600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>915100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>738700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>906700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>572500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>310200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>290800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>285000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>221700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>127600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>48900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15600</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1035500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1060400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1144700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>913200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>736900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>904800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>576900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>309500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>299600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>281200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>221300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>131700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>48900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-22800</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E32" s="3">
         <v>19500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>34300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>98800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-19900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-17400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-21800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-23000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-48200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-15900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1035500</v>
+      </c>
+      <c r="E33" s="3">
         <v>1060400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1144700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>913200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>736900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>904800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>576900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>309500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>299600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>281200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>221300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>131700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>48900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-22800</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1035500</v>
+      </c>
+      <c r="E35" s="3">
         <v>1060400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1144700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>913200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>736900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>904800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>576900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>309500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>299600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>281200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>221300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>131700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>48900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-22800</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,334 +2158,353 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3287000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3610300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3584100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3180800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2565500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1837400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>944100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1387200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1532900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>567500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>462800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>750000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>50900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6500</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>832600</v>
+      </c>
+      <c r="E42" s="3">
         <v>263700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>350300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>322800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>959300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1151600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>485000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>337500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>37800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>92800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>251600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>590000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>58700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>12400</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>545300</v>
+      </c>
+      <c r="E43" s="3">
         <v>455200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>341400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>308800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>315900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>304000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>486000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1178400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>863500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>627400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>306300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>155700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>799800</v>
+      </c>
+      <c r="E44" s="3">
         <v>731800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>853100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>865000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1141400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1263800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1107100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>780500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1069700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>683300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>635700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>561800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>41100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>20700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>10100</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E45" s="3">
         <v>22300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>32800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>36100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>40200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>84600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>111700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>199700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>417600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>42400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>35400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>52700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4400</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5658100</v>
+      </c>
+      <c r="E46" s="3">
         <v>5179100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5297000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4891000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5169800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4774800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3307200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3973100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3983000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2013300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1691700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2069800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>157700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>54800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>23000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1134800</v>
+      </c>
+      <c r="E47" s="3">
         <v>734000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>715200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>699300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>780700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>736900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>734700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>310900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>92300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>138700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>140900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>61100</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
@@ -2408,105 +2512,114 @@
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2675000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2565600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2458900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2481800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2443900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2322900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1863100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1240500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1023700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>616900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>410600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>598500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1300</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1645000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1612500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1582400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1265800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1184100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1070600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>878200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>669700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>591100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>150800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>118800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>172100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>800</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E52" s="3">
         <v>82100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>49100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>56300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>100000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>41100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>84200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>545400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>427000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>64500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>600</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11272300</v>
+      </c>
+      <c r="E54" s="3">
         <v>10266500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10199400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9493100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9805000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9028100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6977400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6333900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5837500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3465000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2788900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2653900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>163100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>57200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>24400</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,248 +2914,264 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1806900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2095400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2449100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2198700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2125500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2385500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2057300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1738000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1769000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1150700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>925000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>958300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>72500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>27800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12800</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>865200</v>
+      </c>
+      <c r="E58" s="3">
         <v>364800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>239000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>429400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>378000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>215100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>204900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>965400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>256200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>13200</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>1800</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1176000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1081400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>988400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>887800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>825600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>719500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>602000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>526900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>615700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>863000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>755300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>998000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>53500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7400</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4415400</v>
+      </c>
+      <c r="E60" s="3">
         <v>4100100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4318800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4135900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4056800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4069600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3436200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3772500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2959700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2013700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1693500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1589900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>126100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>45400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21700</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>79600</v>
+      </c>
+      <c r="E61" s="3">
         <v>81100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>97200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>120800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>150000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>208500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>209700</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>629300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>605000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>564900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>603500</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3039,14 +3184,14 @@
       <c r="F62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3">
         <v>42800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18600</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
@@ -3054,17 +3199,17 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>48000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>27600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>38000</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>8</v>
@@ -3072,9 +3217,12 @@
       <c r="Q62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4918200</v>
+      </c>
+      <c r="E66" s="3">
         <v>4574100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4761400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4552900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4479900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4527000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3781900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3831500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3647400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2673500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2296300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2254000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>126100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21700</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3426,11 +3593,14 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>8900</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6947200</v>
+      </c>
+      <c r="E72" s="3">
         <v>5878300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5195000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4164100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3529500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2717300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1712500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1149700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>861100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>504400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>225000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-18800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-25300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-24200</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5862500</v>
+      </c>
+      <c r="E76" s="3">
         <v>5475900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5212500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4748600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5136900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4365100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3134800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2509800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2196900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>791500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>492700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>399900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>37000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-6200</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1035500</v>
+      </c>
+      <c r="E81" s="3">
         <v>1060400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1144700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>913200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>736900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>904800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>576900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>309500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>299600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>281200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>221300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>131700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>48900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-22800</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>218200</v>
+      </c>
+      <c r="E83" s="3">
         <v>194300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>183200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>178500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>172700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>148600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>119300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>112000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>110800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>139800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>81300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>56500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1065700</v>
+      </c>
+      <c r="E89" s="3">
         <v>1250700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2032800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1525200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1061700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1810600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1765100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>835400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>150800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>391000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>266600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>510800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>66500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>16000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>200</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-283900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-373100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-305600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-352400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-430100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-342700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-474400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-366400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-337800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-321700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-266200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1400</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1186200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-488500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-727700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>152100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-366200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1025500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1183500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-973300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-312400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-230500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-408900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-665900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-48800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3500</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,17 +4686,18 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>256700</v>
+      </c>
+      <c r="E96" s="3">
         <v>230800</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -4501,9 +4734,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-276700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-680800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-866700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-808100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-898600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>85300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1101900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-54300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-75000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>603100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>14100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>7200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>9700</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E101" s="3">
         <v>8700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>12100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-16100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>25800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>13200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-15200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-404800</v>
+      </c>
+      <c r="E102" s="3">
         <v>90000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>450400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>860100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>686300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>780000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-333100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-26700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>939400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>108400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-204100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>432800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>32000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>11400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6400</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
